--- a/output/version3/test/15-5/MARL/IL/RL-RL with pt/(RL+RL) test results.xlsx
+++ b/output/version3/test/15-5/MARL/IL/RL-RL with pt/(RL+RL) test results.xlsx
@@ -471,37 +471,37 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>674</v>
+        <v>589</v>
       </c>
       <c r="C2" t="n">
-        <v>525</v>
+        <v>616</v>
       </c>
       <c r="D2" t="n">
-        <v>545</v>
+        <v>582</v>
       </c>
       <c r="E2" t="n">
-        <v>580</v>
+        <v>588</v>
       </c>
       <c r="F2" t="n">
-        <v>562</v>
+        <v>593</v>
       </c>
       <c r="G2" t="n">
-        <v>585</v>
+        <v>555</v>
       </c>
       <c r="H2" t="n">
-        <v>640</v>
+        <v>652</v>
       </c>
       <c r="I2" t="n">
-        <v>610</v>
+        <v>567</v>
       </c>
       <c r="J2" t="n">
-        <v>581</v>
+        <v>606</v>
       </c>
       <c r="K2" t="n">
-        <v>693</v>
+        <v>627</v>
       </c>
       <c r="L2" t="n">
-        <v>599.5</v>
+        <v>597.5</v>
       </c>
     </row>
     <row r="3">
@@ -509,37 +509,37 @@
         <v>10</v>
       </c>
       <c r="B3" t="n">
-        <v>787</v>
+        <v>724</v>
       </c>
       <c r="C3" t="n">
-        <v>740</v>
+        <v>716</v>
       </c>
       <c r="D3" t="n">
-        <v>721</v>
+        <v>823</v>
       </c>
       <c r="E3" t="n">
-        <v>810</v>
+        <v>744</v>
       </c>
       <c r="F3" t="n">
-        <v>665</v>
+        <v>706</v>
       </c>
       <c r="G3" t="n">
-        <v>773</v>
+        <v>783</v>
       </c>
       <c r="H3" t="n">
-        <v>770</v>
+        <v>811</v>
       </c>
       <c r="I3" t="n">
-        <v>779</v>
+        <v>701</v>
       </c>
       <c r="J3" t="n">
-        <v>696</v>
+        <v>744</v>
       </c>
       <c r="K3" t="n">
-        <v>718</v>
+        <v>671</v>
       </c>
       <c r="L3" t="n">
-        <v>745.9</v>
+        <v>742.3</v>
       </c>
     </row>
     <row r="4">
@@ -547,37 +547,37 @@
         <v>11</v>
       </c>
       <c r="B4" t="n">
-        <v>879</v>
+        <v>753</v>
       </c>
       <c r="C4" t="n">
-        <v>811</v>
+        <v>731</v>
       </c>
       <c r="D4" t="n">
-        <v>619</v>
+        <v>649</v>
       </c>
       <c r="E4" t="n">
-        <v>815</v>
+        <v>781</v>
       </c>
       <c r="F4" t="n">
-        <v>632</v>
+        <v>740</v>
       </c>
       <c r="G4" t="n">
-        <v>688</v>
+        <v>671</v>
       </c>
       <c r="H4" t="n">
-        <v>722</v>
+        <v>692</v>
       </c>
       <c r="I4" t="n">
-        <v>729</v>
+        <v>703</v>
       </c>
       <c r="J4" t="n">
-        <v>725</v>
+        <v>656</v>
       </c>
       <c r="K4" t="n">
-        <v>733</v>
+        <v>702</v>
       </c>
       <c r="L4" t="n">
-        <v>735.3</v>
+        <v>707.8</v>
       </c>
     </row>
     <row r="5">
@@ -585,37 +585,37 @@
         <v>12</v>
       </c>
       <c r="B5" t="n">
-        <v>811</v>
+        <v>870</v>
       </c>
       <c r="C5" t="n">
-        <v>819</v>
+        <v>795</v>
       </c>
       <c r="D5" t="n">
-        <v>866</v>
+        <v>845</v>
       </c>
       <c r="E5" t="n">
-        <v>741</v>
+        <v>815</v>
       </c>
       <c r="F5" t="n">
-        <v>785</v>
+        <v>738</v>
       </c>
       <c r="G5" t="n">
-        <v>799</v>
+        <v>868</v>
       </c>
       <c r="H5" t="n">
-        <v>763</v>
+        <v>724</v>
       </c>
       <c r="I5" t="n">
-        <v>969</v>
+        <v>805</v>
       </c>
       <c r="J5" t="n">
-        <v>835</v>
+        <v>739</v>
       </c>
       <c r="K5" t="n">
-        <v>896</v>
+        <v>759</v>
       </c>
       <c r="L5" t="n">
-        <v>828.4</v>
+        <v>795.8</v>
       </c>
     </row>
     <row r="6">
@@ -623,37 +623,37 @@
         <v>13</v>
       </c>
       <c r="B6" t="n">
-        <v>640</v>
+        <v>587</v>
       </c>
       <c r="C6" t="n">
+        <v>625</v>
+      </c>
+      <c r="D6" t="n">
+        <v>661</v>
+      </c>
+      <c r="E6" t="n">
+        <v>648</v>
+      </c>
+      <c r="F6" t="n">
+        <v>653</v>
+      </c>
+      <c r="G6" t="n">
+        <v>609</v>
+      </c>
+      <c r="H6" t="n">
         <v>662</v>
       </c>
-      <c r="D6" t="n">
-        <v>683</v>
-      </c>
-      <c r="E6" t="n">
-        <v>610</v>
-      </c>
-      <c r="F6" t="n">
-        <v>608</v>
-      </c>
-      <c r="G6" t="n">
-        <v>635</v>
-      </c>
-      <c r="H6" t="n">
-        <v>563</v>
-      </c>
       <c r="I6" t="n">
-        <v>681</v>
+        <v>700</v>
       </c>
       <c r="J6" t="n">
-        <v>719</v>
+        <v>637</v>
       </c>
       <c r="K6" t="n">
-        <v>688</v>
+        <v>598</v>
       </c>
       <c r="L6" t="n">
-        <v>648.9</v>
+        <v>638</v>
       </c>
     </row>
     <row r="7">
@@ -661,37 +661,37 @@
         <v>14</v>
       </c>
       <c r="B7" t="n">
-        <v>795</v>
+        <v>780</v>
       </c>
       <c r="C7" t="n">
-        <v>788</v>
+        <v>826</v>
       </c>
       <c r="D7" t="n">
-        <v>772</v>
+        <v>776</v>
       </c>
       <c r="E7" t="n">
-        <v>805</v>
+        <v>769</v>
       </c>
       <c r="F7" t="n">
-        <v>802</v>
+        <v>700</v>
       </c>
       <c r="G7" t="n">
-        <v>812</v>
+        <v>704</v>
       </c>
       <c r="H7" t="n">
-        <v>832</v>
+        <v>799</v>
       </c>
       <c r="I7" t="n">
-        <v>745</v>
+        <v>849</v>
       </c>
       <c r="J7" t="n">
-        <v>844</v>
+        <v>738</v>
       </c>
       <c r="K7" t="n">
-        <v>745</v>
+        <v>729</v>
       </c>
       <c r="L7" t="n">
-        <v>794</v>
+        <v>767</v>
       </c>
     </row>
     <row r="8">
@@ -699,37 +699,37 @@
         <v>15</v>
       </c>
       <c r="B8" t="n">
-        <v>647</v>
+        <v>678</v>
       </c>
       <c r="C8" t="n">
-        <v>658</v>
+        <v>661</v>
       </c>
       <c r="D8" t="n">
-        <v>662</v>
+        <v>673</v>
       </c>
       <c r="E8" t="n">
-        <v>705</v>
+        <v>700</v>
       </c>
       <c r="F8" t="n">
-        <v>648</v>
+        <v>680</v>
       </c>
       <c r="G8" t="n">
-        <v>771</v>
+        <v>613</v>
       </c>
       <c r="H8" t="n">
-        <v>676</v>
+        <v>672</v>
       </c>
       <c r="I8" t="n">
-        <v>594</v>
+        <v>666</v>
       </c>
       <c r="J8" t="n">
-        <v>717</v>
+        <v>727</v>
       </c>
       <c r="K8" t="n">
-        <v>735</v>
+        <v>619</v>
       </c>
       <c r="L8" t="n">
-        <v>681.3</v>
+        <v>668.9</v>
       </c>
     </row>
     <row r="9">
@@ -737,37 +737,37 @@
         <v>16</v>
       </c>
       <c r="B9" t="n">
-        <v>613</v>
+        <v>725</v>
       </c>
       <c r="C9" t="n">
-        <v>675</v>
+        <v>716</v>
       </c>
       <c r="D9" t="n">
-        <v>703</v>
+        <v>643</v>
       </c>
       <c r="E9" t="n">
-        <v>679</v>
+        <v>676</v>
       </c>
       <c r="F9" t="n">
-        <v>633</v>
+        <v>611</v>
       </c>
       <c r="G9" t="n">
-        <v>566</v>
+        <v>733</v>
       </c>
       <c r="H9" t="n">
-        <v>625</v>
+        <v>652</v>
       </c>
       <c r="I9" t="n">
-        <v>669</v>
+        <v>656</v>
       </c>
       <c r="J9" t="n">
-        <v>562</v>
+        <v>693</v>
       </c>
       <c r="K9" t="n">
-        <v>697</v>
+        <v>687</v>
       </c>
       <c r="L9" t="n">
-        <v>642.2</v>
+        <v>679.2</v>
       </c>
     </row>
     <row r="10">
@@ -775,37 +775,37 @@
         <v>17</v>
       </c>
       <c r="B10" t="n">
+        <v>775</v>
+      </c>
+      <c r="C10" t="n">
+        <v>773</v>
+      </c>
+      <c r="D10" t="n">
+        <v>784</v>
+      </c>
+      <c r="E10" t="n">
+        <v>752</v>
+      </c>
+      <c r="F10" t="n">
+        <v>816</v>
+      </c>
+      <c r="G10" t="n">
         <v>830</v>
       </c>
-      <c r="C10" t="n">
-        <v>918</v>
-      </c>
-      <c r="D10" t="n">
-        <v>794</v>
-      </c>
-      <c r="E10" t="n">
-        <v>760</v>
-      </c>
-      <c r="F10" t="n">
-        <v>726</v>
-      </c>
-      <c r="G10" t="n">
-        <v>773</v>
-      </c>
       <c r="H10" t="n">
-        <v>689</v>
+        <v>740</v>
       </c>
       <c r="I10" t="n">
-        <v>828</v>
+        <v>804</v>
       </c>
       <c r="J10" t="n">
-        <v>782</v>
+        <v>662</v>
       </c>
       <c r="K10" t="n">
-        <v>796</v>
+        <v>849</v>
       </c>
       <c r="L10" t="n">
-        <v>789.6</v>
+        <v>778.5</v>
       </c>
     </row>
     <row r="11">
@@ -813,37 +813,37 @@
         <v>18</v>
       </c>
       <c r="B11" t="n">
-        <v>684</v>
+        <v>719</v>
       </c>
       <c r="C11" t="n">
-        <v>822</v>
+        <v>793</v>
       </c>
       <c r="D11" t="n">
-        <v>701</v>
+        <v>688</v>
       </c>
       <c r="E11" t="n">
-        <v>670</v>
+        <v>797</v>
       </c>
       <c r="F11" t="n">
-        <v>670</v>
+        <v>694</v>
       </c>
       <c r="G11" t="n">
+        <v>873</v>
+      </c>
+      <c r="H11" t="n">
+        <v>679</v>
+      </c>
+      <c r="I11" t="n">
         <v>729</v>
       </c>
-      <c r="H11" t="n">
-        <v>685</v>
-      </c>
-      <c r="I11" t="n">
-        <v>775</v>
-      </c>
       <c r="J11" t="n">
-        <v>804</v>
+        <v>715</v>
       </c>
       <c r="K11" t="n">
-        <v>728</v>
+        <v>686</v>
       </c>
       <c r="L11" t="n">
-        <v>726.8</v>
+        <v>737.3</v>
       </c>
     </row>
     <row r="12">
@@ -851,37 +851,37 @@
         <v>19</v>
       </c>
       <c r="B12" t="n">
-        <v>707</v>
+        <v>671</v>
       </c>
       <c r="C12" t="n">
-        <v>709</v>
+        <v>686</v>
       </c>
       <c r="D12" t="n">
-        <v>658</v>
+        <v>671</v>
       </c>
       <c r="E12" t="n">
-        <v>745</v>
+        <v>717</v>
       </c>
       <c r="F12" t="n">
-        <v>689</v>
+        <v>717</v>
       </c>
       <c r="G12" t="n">
-        <v>655</v>
+        <v>692</v>
       </c>
       <c r="H12" t="n">
-        <v>644</v>
+        <v>671</v>
       </c>
       <c r="I12" t="n">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="J12" t="n">
-        <v>719</v>
+        <v>673</v>
       </c>
       <c r="K12" t="n">
-        <v>646</v>
+        <v>637</v>
       </c>
       <c r="L12" t="n">
-        <v>680.7</v>
+        <v>676.9</v>
       </c>
     </row>
     <row r="13">
@@ -889,37 +889,37 @@
         <v>2</v>
       </c>
       <c r="B13" t="n">
-        <v>564</v>
+        <v>572</v>
       </c>
       <c r="C13" t="n">
-        <v>569</v>
+        <v>551</v>
       </c>
       <c r="D13" t="n">
-        <v>511</v>
+        <v>541</v>
       </c>
       <c r="E13" t="n">
-        <v>529</v>
+        <v>577</v>
       </c>
       <c r="F13" t="n">
-        <v>607</v>
+        <v>517</v>
       </c>
       <c r="G13" t="n">
-        <v>522</v>
+        <v>574</v>
       </c>
       <c r="H13" t="n">
-        <v>669</v>
+        <v>555</v>
       </c>
       <c r="I13" t="n">
-        <v>575</v>
+        <v>632</v>
       </c>
       <c r="J13" t="n">
-        <v>574</v>
+        <v>548</v>
       </c>
       <c r="K13" t="n">
-        <v>713</v>
+        <v>570</v>
       </c>
       <c r="L13" t="n">
-        <v>583.3</v>
+        <v>563.7</v>
       </c>
     </row>
     <row r="14">
@@ -927,37 +927,37 @@
         <v>20</v>
       </c>
       <c r="B14" t="n">
-        <v>647</v>
+        <v>693</v>
       </c>
       <c r="C14" t="n">
-        <v>669</v>
+        <v>681</v>
       </c>
       <c r="D14" t="n">
-        <v>678</v>
+        <v>656</v>
       </c>
       <c r="E14" t="n">
-        <v>671</v>
+        <v>617</v>
       </c>
       <c r="F14" t="n">
-        <v>608</v>
+        <v>625</v>
       </c>
       <c r="G14" t="n">
-        <v>690</v>
+        <v>639</v>
       </c>
       <c r="H14" t="n">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="I14" t="n">
-        <v>621</v>
+        <v>619</v>
       </c>
       <c r="J14" t="n">
-        <v>674</v>
+        <v>698</v>
       </c>
       <c r="K14" t="n">
-        <v>615</v>
+        <v>661</v>
       </c>
       <c r="L14" t="n">
-        <v>655.1</v>
+        <v>656.5</v>
       </c>
     </row>
     <row r="15">
@@ -965,37 +965,37 @@
         <v>21</v>
       </c>
       <c r="B15" t="n">
-        <v>780</v>
+        <v>716</v>
       </c>
       <c r="C15" t="n">
-        <v>723</v>
+        <v>681</v>
       </c>
       <c r="D15" t="n">
-        <v>743</v>
+        <v>737</v>
       </c>
       <c r="E15" t="n">
-        <v>836</v>
+        <v>642</v>
       </c>
       <c r="F15" t="n">
-        <v>685</v>
+        <v>703</v>
       </c>
       <c r="G15" t="n">
-        <v>693</v>
+        <v>663</v>
       </c>
       <c r="H15" t="n">
-        <v>729</v>
+        <v>688</v>
       </c>
       <c r="I15" t="n">
-        <v>692</v>
+        <v>675</v>
       </c>
       <c r="J15" t="n">
-        <v>795</v>
+        <v>739</v>
       </c>
       <c r="K15" t="n">
-        <v>727</v>
+        <v>724</v>
       </c>
       <c r="L15" t="n">
-        <v>740.3</v>
+        <v>696.8</v>
       </c>
     </row>
     <row r="16">
@@ -1003,37 +1003,37 @@
         <v>22</v>
       </c>
       <c r="B16" t="n">
-        <v>653</v>
+        <v>681</v>
       </c>
       <c r="C16" t="n">
+        <v>655</v>
+      </c>
+      <c r="D16" t="n">
+        <v>627</v>
+      </c>
+      <c r="E16" t="n">
+        <v>685</v>
+      </c>
+      <c r="F16" t="n">
+        <v>671</v>
+      </c>
+      <c r="G16" t="n">
+        <v>698</v>
+      </c>
+      <c r="H16" t="n">
         <v>697</v>
       </c>
-      <c r="D16" t="n">
-        <v>668</v>
-      </c>
-      <c r="E16" t="n">
-        <v>672</v>
-      </c>
-      <c r="F16" t="n">
-        <v>685</v>
-      </c>
-      <c r="G16" t="n">
-        <v>692</v>
-      </c>
-      <c r="H16" t="n">
-        <v>616</v>
-      </c>
       <c r="I16" t="n">
-        <v>737</v>
+        <v>628</v>
       </c>
       <c r="J16" t="n">
-        <v>685</v>
+        <v>696</v>
       </c>
       <c r="K16" t="n">
-        <v>687</v>
+        <v>761</v>
       </c>
       <c r="L16" t="n">
-        <v>679.2</v>
+        <v>679.9</v>
       </c>
     </row>
     <row r="17">
@@ -1041,37 +1041,37 @@
         <v>23</v>
       </c>
       <c r="B17" t="n">
-        <v>771</v>
+        <v>730</v>
       </c>
       <c r="C17" t="n">
-        <v>771</v>
+        <v>815</v>
       </c>
       <c r="D17" t="n">
-        <v>813</v>
+        <v>654</v>
       </c>
       <c r="E17" t="n">
-        <v>753</v>
+        <v>711</v>
       </c>
       <c r="F17" t="n">
-        <v>856</v>
+        <v>853</v>
       </c>
       <c r="G17" t="n">
-        <v>684</v>
+        <v>871</v>
       </c>
       <c r="H17" t="n">
-        <v>818</v>
+        <v>763</v>
       </c>
       <c r="I17" t="n">
-        <v>776</v>
+        <v>743</v>
       </c>
       <c r="J17" t="n">
-        <v>767</v>
+        <v>698</v>
       </c>
       <c r="K17" t="n">
-        <v>747</v>
+        <v>907</v>
       </c>
       <c r="L17" t="n">
-        <v>775.6</v>
+        <v>774.5</v>
       </c>
     </row>
     <row r="18">
@@ -1079,37 +1079,37 @@
         <v>24</v>
       </c>
       <c r="B18" t="n">
-        <v>562</v>
+        <v>626</v>
       </c>
       <c r="C18" t="n">
-        <v>654</v>
+        <v>627</v>
       </c>
       <c r="D18" t="n">
-        <v>734</v>
+        <v>606</v>
       </c>
       <c r="E18" t="n">
-        <v>657</v>
+        <v>625</v>
       </c>
       <c r="F18" t="n">
+        <v>702</v>
+      </c>
+      <c r="G18" t="n">
+        <v>649</v>
+      </c>
+      <c r="H18" t="n">
+        <v>723</v>
+      </c>
+      <c r="I18" t="n">
+        <v>676</v>
+      </c>
+      <c r="J18" t="n">
         <v>674</v>
       </c>
-      <c r="G18" t="n">
-        <v>653</v>
-      </c>
-      <c r="H18" t="n">
-        <v>635</v>
-      </c>
-      <c r="I18" t="n">
-        <v>620</v>
-      </c>
-      <c r="J18" t="n">
-        <v>645</v>
-      </c>
       <c r="K18" t="n">
-        <v>633</v>
+        <v>697</v>
       </c>
       <c r="L18" t="n">
-        <v>646.7</v>
+        <v>660.5</v>
       </c>
     </row>
     <row r="19">
@@ -1117,37 +1117,37 @@
         <v>25</v>
       </c>
       <c r="B19" t="n">
-        <v>613</v>
+        <v>679</v>
       </c>
       <c r="C19" t="n">
-        <v>693</v>
+        <v>683</v>
       </c>
       <c r="D19" t="n">
-        <v>637</v>
+        <v>643</v>
       </c>
       <c r="E19" t="n">
-        <v>707</v>
+        <v>644</v>
       </c>
       <c r="F19" t="n">
-        <v>697</v>
+        <v>639</v>
       </c>
       <c r="G19" t="n">
-        <v>651</v>
+        <v>675</v>
       </c>
       <c r="H19" t="n">
-        <v>720</v>
+        <v>636</v>
       </c>
       <c r="I19" t="n">
-        <v>613</v>
+        <v>678</v>
       </c>
       <c r="J19" t="n">
-        <v>660</v>
+        <v>691</v>
       </c>
       <c r="K19" t="n">
-        <v>728</v>
+        <v>655</v>
       </c>
       <c r="L19" t="n">
-        <v>671.9</v>
+        <v>662.3</v>
       </c>
     </row>
     <row r="20">
@@ -1155,37 +1155,37 @@
         <v>26</v>
       </c>
       <c r="B20" t="n">
-        <v>575</v>
+        <v>647</v>
       </c>
       <c r="C20" t="n">
-        <v>629</v>
+        <v>667</v>
       </c>
       <c r="D20" t="n">
-        <v>698</v>
+        <v>679</v>
       </c>
       <c r="E20" t="n">
-        <v>740</v>
+        <v>682</v>
       </c>
       <c r="F20" t="n">
-        <v>783</v>
+        <v>655</v>
       </c>
       <c r="G20" t="n">
-        <v>606</v>
+        <v>702</v>
       </c>
       <c r="H20" t="n">
-        <v>629</v>
+        <v>687</v>
       </c>
       <c r="I20" t="n">
-        <v>720</v>
+        <v>682</v>
       </c>
       <c r="J20" t="n">
-        <v>629</v>
+        <v>651</v>
       </c>
       <c r="K20" t="n">
-        <v>691</v>
+        <v>709</v>
       </c>
       <c r="L20" t="n">
-        <v>670</v>
+        <v>676.1</v>
       </c>
     </row>
     <row r="21">
@@ -1193,37 +1193,37 @@
         <v>27</v>
       </c>
       <c r="B21" t="n">
+        <v>685</v>
+      </c>
+      <c r="C21" t="n">
+        <v>587</v>
+      </c>
+      <c r="D21" t="n">
         <v>626</v>
       </c>
-      <c r="C21" t="n">
-        <v>642</v>
-      </c>
-      <c r="D21" t="n">
-        <v>620</v>
-      </c>
       <c r="E21" t="n">
-        <v>701</v>
+        <v>679</v>
       </c>
       <c r="F21" t="n">
-        <v>713</v>
+        <v>684</v>
       </c>
       <c r="G21" t="n">
-        <v>701</v>
+        <v>725</v>
       </c>
       <c r="H21" t="n">
-        <v>712</v>
+        <v>628</v>
       </c>
       <c r="I21" t="n">
-        <v>653</v>
+        <v>640</v>
       </c>
       <c r="J21" t="n">
-        <v>659</v>
+        <v>632</v>
       </c>
       <c r="K21" t="n">
-        <v>645</v>
+        <v>680</v>
       </c>
       <c r="L21" t="n">
-        <v>667.2</v>
+        <v>656.6</v>
       </c>
     </row>
     <row r="22">
@@ -1231,37 +1231,37 @@
         <v>28</v>
       </c>
       <c r="B22" t="n">
-        <v>553</v>
+        <v>617</v>
       </c>
       <c r="C22" t="n">
-        <v>649</v>
+        <v>669</v>
       </c>
       <c r="D22" t="n">
-        <v>624</v>
+        <v>637</v>
       </c>
       <c r="E22" t="n">
-        <v>600</v>
+        <v>523</v>
       </c>
       <c r="F22" t="n">
-        <v>574</v>
+        <v>578</v>
       </c>
       <c r="G22" t="n">
-        <v>531</v>
+        <v>560</v>
       </c>
       <c r="H22" t="n">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="I22" t="n">
         <v>598</v>
       </c>
       <c r="J22" t="n">
-        <v>621</v>
+        <v>677</v>
       </c>
       <c r="K22" t="n">
-        <v>620</v>
+        <v>618</v>
       </c>
       <c r="L22" t="n">
-        <v>598.5</v>
+        <v>608.9</v>
       </c>
     </row>
     <row r="23">
@@ -1269,37 +1269,37 @@
         <v>29</v>
       </c>
       <c r="B23" t="n">
-        <v>793</v>
+        <v>687</v>
       </c>
       <c r="C23" t="n">
-        <v>824</v>
+        <v>773</v>
       </c>
       <c r="D23" t="n">
-        <v>688</v>
+        <v>758</v>
       </c>
       <c r="E23" t="n">
-        <v>700</v>
+        <v>633</v>
       </c>
       <c r="F23" t="n">
-        <v>675</v>
+        <v>683</v>
       </c>
       <c r="G23" t="n">
-        <v>691</v>
+        <v>701</v>
       </c>
       <c r="H23" t="n">
-        <v>804</v>
+        <v>742</v>
       </c>
       <c r="I23" t="n">
-        <v>673</v>
+        <v>731</v>
       </c>
       <c r="J23" t="n">
-        <v>738</v>
+        <v>629</v>
       </c>
       <c r="K23" t="n">
-        <v>608</v>
+        <v>716</v>
       </c>
       <c r="L23" t="n">
-        <v>719.4</v>
+        <v>705.3</v>
       </c>
     </row>
     <row r="24">
@@ -1307,37 +1307,37 @@
         <v>3</v>
       </c>
       <c r="B24" t="n">
-        <v>802</v>
+        <v>742</v>
       </c>
       <c r="C24" t="n">
-        <v>654</v>
+        <v>684</v>
       </c>
       <c r="D24" t="n">
-        <v>644</v>
+        <v>649</v>
       </c>
       <c r="E24" t="n">
-        <v>620</v>
+        <v>863</v>
       </c>
       <c r="F24" t="n">
-        <v>724</v>
+        <v>591</v>
       </c>
       <c r="G24" t="n">
-        <v>665</v>
+        <v>657</v>
       </c>
       <c r="H24" t="n">
-        <v>656</v>
+        <v>741</v>
       </c>
       <c r="I24" t="n">
-        <v>754</v>
+        <v>736</v>
       </c>
       <c r="J24" t="n">
-        <v>735</v>
+        <v>706</v>
       </c>
       <c r="K24" t="n">
-        <v>633</v>
+        <v>691</v>
       </c>
       <c r="L24" t="n">
-        <v>688.7</v>
+        <v>706</v>
       </c>
     </row>
     <row r="25">
@@ -1345,37 +1345,37 @@
         <v>30</v>
       </c>
       <c r="B25" t="n">
-        <v>699</v>
+        <v>642</v>
       </c>
       <c r="C25" t="n">
-        <v>682</v>
+        <v>663</v>
       </c>
       <c r="D25" t="n">
-        <v>649</v>
+        <v>690</v>
       </c>
       <c r="E25" t="n">
-        <v>639</v>
+        <v>683</v>
       </c>
       <c r="F25" t="n">
-        <v>600</v>
+        <v>586</v>
       </c>
       <c r="G25" t="n">
-        <v>647</v>
+        <v>627</v>
       </c>
       <c r="H25" t="n">
-        <v>685</v>
+        <v>642</v>
       </c>
       <c r="I25" t="n">
-        <v>603</v>
+        <v>678</v>
       </c>
       <c r="J25" t="n">
-        <v>685</v>
+        <v>666</v>
       </c>
       <c r="K25" t="n">
-        <v>652</v>
+        <v>610</v>
       </c>
       <c r="L25" t="n">
-        <v>654.1</v>
+        <v>648.7</v>
       </c>
     </row>
     <row r="26">
@@ -1383,37 +1383,37 @@
         <v>31</v>
       </c>
       <c r="B26" t="n">
-        <v>743</v>
+        <v>602</v>
       </c>
       <c r="C26" t="n">
-        <v>640</v>
+        <v>739</v>
       </c>
       <c r="D26" t="n">
-        <v>691</v>
+        <v>697</v>
       </c>
       <c r="E26" t="n">
-        <v>717</v>
+        <v>724</v>
       </c>
       <c r="F26" t="n">
-        <v>754</v>
+        <v>835</v>
       </c>
       <c r="G26" t="n">
-        <v>746</v>
+        <v>773</v>
       </c>
       <c r="H26" t="n">
-        <v>742</v>
+        <v>718</v>
       </c>
       <c r="I26" t="n">
-        <v>791</v>
+        <v>706</v>
       </c>
       <c r="J26" t="n">
-        <v>706</v>
+        <v>666</v>
       </c>
       <c r="K26" t="n">
-        <v>737</v>
+        <v>733</v>
       </c>
       <c r="L26" t="n">
-        <v>726.7</v>
+        <v>719.3</v>
       </c>
     </row>
     <row r="27">
@@ -1421,37 +1421,37 @@
         <v>32</v>
       </c>
       <c r="B27" t="n">
-        <v>835</v>
+        <v>732</v>
       </c>
       <c r="C27" t="n">
-        <v>712</v>
+        <v>728</v>
       </c>
       <c r="D27" t="n">
-        <v>734</v>
+        <v>771</v>
       </c>
       <c r="E27" t="n">
-        <v>676</v>
+        <v>699</v>
       </c>
       <c r="F27" t="n">
-        <v>711</v>
+        <v>698</v>
       </c>
       <c r="G27" t="n">
-        <v>796</v>
+        <v>846</v>
       </c>
       <c r="H27" t="n">
-        <v>694</v>
+        <v>733</v>
       </c>
       <c r="I27" t="n">
-        <v>744</v>
+        <v>705</v>
       </c>
       <c r="J27" t="n">
-        <v>714</v>
+        <v>729</v>
       </c>
       <c r="K27" t="n">
-        <v>704</v>
+        <v>666</v>
       </c>
       <c r="L27" t="n">
-        <v>732</v>
+        <v>730.7</v>
       </c>
     </row>
     <row r="28">
@@ -1459,37 +1459,37 @@
         <v>33</v>
       </c>
       <c r="B28" t="n">
-        <v>691</v>
+        <v>607</v>
       </c>
       <c r="C28" t="n">
-        <v>600</v>
+        <v>650</v>
       </c>
       <c r="D28" t="n">
+        <v>669</v>
+      </c>
+      <c r="E28" t="n">
+        <v>697</v>
+      </c>
+      <c r="F28" t="n">
+        <v>564</v>
+      </c>
+      <c r="G28" t="n">
+        <v>629</v>
+      </c>
+      <c r="H28" t="n">
+        <v>599</v>
+      </c>
+      <c r="I28" t="n">
+        <v>614</v>
+      </c>
+      <c r="J28" t="n">
         <v>656</v>
       </c>
-      <c r="E28" t="n">
-        <v>605</v>
-      </c>
-      <c r="F28" t="n">
-        <v>627</v>
-      </c>
-      <c r="G28" t="n">
-        <v>668</v>
-      </c>
-      <c r="H28" t="n">
-        <v>628</v>
-      </c>
-      <c r="I28" t="n">
-        <v>620</v>
-      </c>
-      <c r="J28" t="n">
-        <v>602</v>
-      </c>
       <c r="K28" t="n">
-        <v>620</v>
+        <v>630</v>
       </c>
       <c r="L28" t="n">
-        <v>631.7</v>
+        <v>631.5</v>
       </c>
     </row>
     <row r="29">
@@ -1497,37 +1497,37 @@
         <v>34</v>
       </c>
       <c r="B29" t="n">
+        <v>671</v>
+      </c>
+      <c r="C29" t="n">
+        <v>643</v>
+      </c>
+      <c r="D29" t="n">
+        <v>629</v>
+      </c>
+      <c r="E29" t="n">
+        <v>699</v>
+      </c>
+      <c r="F29" t="n">
+        <v>692</v>
+      </c>
+      <c r="G29" t="n">
+        <v>683</v>
+      </c>
+      <c r="H29" t="n">
+        <v>635</v>
+      </c>
+      <c r="I29" t="n">
         <v>652</v>
       </c>
-      <c r="C29" t="n">
-        <v>711</v>
-      </c>
-      <c r="D29" t="n">
-        <v>647</v>
-      </c>
-      <c r="E29" t="n">
-        <v>656</v>
-      </c>
-      <c r="F29" t="n">
-        <v>688</v>
-      </c>
-      <c r="G29" t="n">
-        <v>707</v>
-      </c>
-      <c r="H29" t="n">
-        <v>699</v>
-      </c>
-      <c r="I29" t="n">
-        <v>721</v>
-      </c>
       <c r="J29" t="n">
-        <v>629</v>
+        <v>696</v>
       </c>
       <c r="K29" t="n">
-        <v>698</v>
+        <v>740</v>
       </c>
       <c r="L29" t="n">
-        <v>680.8</v>
+        <v>674</v>
       </c>
     </row>
     <row r="30">
@@ -1535,37 +1535,37 @@
         <v>35</v>
       </c>
       <c r="B30" t="n">
-        <v>736</v>
+        <v>787</v>
       </c>
       <c r="C30" t="n">
-        <v>681</v>
+        <v>609</v>
       </c>
       <c r="D30" t="n">
-        <v>635</v>
+        <v>606</v>
       </c>
       <c r="E30" t="n">
-        <v>679</v>
+        <v>623</v>
       </c>
       <c r="F30" t="n">
-        <v>643</v>
+        <v>630</v>
       </c>
       <c r="G30" t="n">
-        <v>618</v>
+        <v>711</v>
       </c>
       <c r="H30" t="n">
-        <v>691</v>
+        <v>740</v>
       </c>
       <c r="I30" t="n">
-        <v>696</v>
+        <v>812</v>
       </c>
       <c r="J30" t="n">
-        <v>826</v>
+        <v>710</v>
       </c>
       <c r="K30" t="n">
-        <v>847</v>
+        <v>676</v>
       </c>
       <c r="L30" t="n">
-        <v>705.2</v>
+        <v>690.4</v>
       </c>
     </row>
     <row r="31">
@@ -1573,37 +1573,37 @@
         <v>36</v>
       </c>
       <c r="B31" t="n">
-        <v>748</v>
+        <v>656</v>
       </c>
       <c r="C31" t="n">
-        <v>705</v>
+        <v>723</v>
       </c>
       <c r="D31" t="n">
-        <v>624</v>
+        <v>698</v>
       </c>
       <c r="E31" t="n">
+        <v>638</v>
+      </c>
+      <c r="F31" t="n">
+        <v>623</v>
+      </c>
+      <c r="G31" t="n">
+        <v>686</v>
+      </c>
+      <c r="H31" t="n">
+        <v>663</v>
+      </c>
+      <c r="I31" t="n">
         <v>672</v>
       </c>
-      <c r="F31" t="n">
-        <v>675</v>
-      </c>
-      <c r="G31" t="n">
-        <v>677</v>
-      </c>
-      <c r="H31" t="n">
-        <v>622</v>
-      </c>
-      <c r="I31" t="n">
-        <v>620</v>
-      </c>
       <c r="J31" t="n">
-        <v>692</v>
+        <v>740</v>
       </c>
       <c r="K31" t="n">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="L31" t="n">
-        <v>668.6</v>
+        <v>674.8</v>
       </c>
     </row>
     <row r="32">
@@ -1611,37 +1611,37 @@
         <v>37</v>
       </c>
       <c r="B32" t="n">
+        <v>647</v>
+      </c>
+      <c r="C32" t="n">
+        <v>626</v>
+      </c>
+      <c r="D32" t="n">
+        <v>568</v>
+      </c>
+      <c r="E32" t="n">
         <v>658</v>
       </c>
-      <c r="C32" t="n">
-        <v>650</v>
-      </c>
-      <c r="D32" t="n">
-        <v>687</v>
-      </c>
-      <c r="E32" t="n">
-        <v>572</v>
-      </c>
       <c r="F32" t="n">
-        <v>655</v>
+        <v>631</v>
       </c>
       <c r="G32" t="n">
-        <v>671</v>
+        <v>702</v>
       </c>
       <c r="H32" t="n">
-        <v>684</v>
+        <v>709</v>
       </c>
       <c r="I32" t="n">
-        <v>694</v>
+        <v>534</v>
       </c>
       <c r="J32" t="n">
-        <v>625</v>
+        <v>609</v>
       </c>
       <c r="K32" t="n">
-        <v>503</v>
+        <v>734</v>
       </c>
       <c r="L32" t="n">
-        <v>639.9</v>
+        <v>641.8</v>
       </c>
     </row>
     <row r="33">
@@ -1649,37 +1649,37 @@
         <v>38</v>
       </c>
       <c r="B33" t="n">
-        <v>718</v>
+        <v>698</v>
       </c>
       <c r="C33" t="n">
-        <v>748</v>
+        <v>794</v>
       </c>
       <c r="D33" t="n">
-        <v>791</v>
+        <v>804</v>
       </c>
       <c r="E33" t="n">
-        <v>717</v>
+        <v>727</v>
       </c>
       <c r="F33" t="n">
-        <v>761</v>
+        <v>732</v>
       </c>
       <c r="G33" t="n">
-        <v>687</v>
+        <v>749</v>
       </c>
       <c r="H33" t="n">
-        <v>719</v>
+        <v>895</v>
       </c>
       <c r="I33" t="n">
-        <v>737</v>
+        <v>752</v>
       </c>
       <c r="J33" t="n">
-        <v>698</v>
+        <v>624</v>
       </c>
       <c r="K33" t="n">
-        <v>723</v>
+        <v>721</v>
       </c>
       <c r="L33" t="n">
-        <v>729.9</v>
+        <v>749.6</v>
       </c>
     </row>
     <row r="34">
@@ -1687,37 +1687,37 @@
         <v>39</v>
       </c>
       <c r="B34" t="n">
-        <v>708</v>
+        <v>585</v>
       </c>
       <c r="C34" t="n">
-        <v>567</v>
+        <v>667</v>
       </c>
       <c r="D34" t="n">
-        <v>698</v>
+        <v>606</v>
       </c>
       <c r="E34" t="n">
-        <v>627</v>
+        <v>575</v>
       </c>
       <c r="F34" t="n">
-        <v>649</v>
+        <v>558</v>
       </c>
       <c r="G34" t="n">
-        <v>649</v>
+        <v>628</v>
       </c>
       <c r="H34" t="n">
-        <v>638</v>
+        <v>579</v>
       </c>
       <c r="I34" t="n">
-        <v>643</v>
+        <v>601</v>
       </c>
       <c r="J34" t="n">
-        <v>566</v>
+        <v>626</v>
       </c>
       <c r="K34" t="n">
-        <v>654</v>
+        <v>624</v>
       </c>
       <c r="L34" t="n">
-        <v>639.9</v>
+        <v>604.9</v>
       </c>
     </row>
     <row r="35">
@@ -1725,37 +1725,37 @@
         <v>4</v>
       </c>
       <c r="B35" t="n">
-        <v>710</v>
+        <v>694</v>
       </c>
       <c r="C35" t="n">
-        <v>777</v>
+        <v>754</v>
       </c>
       <c r="D35" t="n">
-        <v>715</v>
+        <v>780</v>
       </c>
       <c r="E35" t="n">
-        <v>800</v>
+        <v>853</v>
       </c>
       <c r="F35" t="n">
-        <v>880</v>
+        <v>761</v>
       </c>
       <c r="G35" t="n">
-        <v>722</v>
+        <v>677</v>
       </c>
       <c r="H35" t="n">
-        <v>773</v>
+        <v>732</v>
       </c>
       <c r="I35" t="n">
-        <v>780</v>
+        <v>665</v>
       </c>
       <c r="J35" t="n">
-        <v>708</v>
+        <v>824</v>
       </c>
       <c r="K35" t="n">
-        <v>789</v>
+        <v>829</v>
       </c>
       <c r="L35" t="n">
-        <v>765.4</v>
+        <v>756.9</v>
       </c>
     </row>
     <row r="36">
@@ -1763,37 +1763,37 @@
         <v>40</v>
       </c>
       <c r="B36" t="n">
-        <v>568</v>
+        <v>577</v>
       </c>
       <c r="C36" t="n">
-        <v>608</v>
+        <v>618</v>
       </c>
       <c r="D36" t="n">
-        <v>565</v>
+        <v>588</v>
       </c>
       <c r="E36" t="n">
-        <v>638</v>
+        <v>643</v>
       </c>
       <c r="F36" t="n">
-        <v>569</v>
+        <v>566</v>
       </c>
       <c r="G36" t="n">
-        <v>618</v>
+        <v>611</v>
       </c>
       <c r="H36" t="n">
-        <v>598</v>
+        <v>614</v>
       </c>
       <c r="I36" t="n">
-        <v>589</v>
+        <v>610</v>
       </c>
       <c r="J36" t="n">
-        <v>568</v>
+        <v>652</v>
       </c>
       <c r="K36" t="n">
-        <v>569</v>
+        <v>630</v>
       </c>
       <c r="L36" t="n">
-        <v>589</v>
+        <v>610.9</v>
       </c>
     </row>
     <row r="37">
@@ -1801,37 +1801,37 @@
         <v>41</v>
       </c>
       <c r="B37" t="n">
-        <v>691</v>
+        <v>655</v>
       </c>
       <c r="C37" t="n">
-        <v>682</v>
+        <v>729</v>
       </c>
       <c r="D37" t="n">
-        <v>714</v>
+        <v>775</v>
       </c>
       <c r="E37" t="n">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="F37" t="n">
-        <v>861</v>
+        <v>675</v>
       </c>
       <c r="G37" t="n">
-        <v>673</v>
+        <v>781</v>
       </c>
       <c r="H37" t="n">
-        <v>717</v>
+        <v>709</v>
       </c>
       <c r="I37" t="n">
-        <v>802</v>
+        <v>711</v>
       </c>
       <c r="J37" t="n">
-        <v>642</v>
+        <v>653</v>
       </c>
       <c r="K37" t="n">
-        <v>742</v>
+        <v>600</v>
       </c>
       <c r="L37" t="n">
-        <v>722.8</v>
+        <v>699.4</v>
       </c>
     </row>
     <row r="38">
@@ -1839,37 +1839,37 @@
         <v>42</v>
       </c>
       <c r="B38" t="n">
-        <v>662</v>
+        <v>710</v>
       </c>
       <c r="C38" t="n">
-        <v>727</v>
+        <v>668</v>
       </c>
       <c r="D38" t="n">
-        <v>658</v>
+        <v>679</v>
       </c>
       <c r="E38" t="n">
-        <v>697</v>
+        <v>751</v>
       </c>
       <c r="F38" t="n">
-        <v>745</v>
+        <v>752</v>
       </c>
       <c r="G38" t="n">
-        <v>717</v>
+        <v>712</v>
       </c>
       <c r="H38" t="n">
-        <v>679</v>
+        <v>673</v>
       </c>
       <c r="I38" t="n">
-        <v>678</v>
+        <v>713</v>
       </c>
       <c r="J38" t="n">
-        <v>698</v>
+        <v>721</v>
       </c>
       <c r="K38" t="n">
-        <v>707</v>
+        <v>699</v>
       </c>
       <c r="L38" t="n">
-        <v>696.8</v>
+        <v>707.8</v>
       </c>
     </row>
     <row r="39">
@@ -1877,37 +1877,37 @@
         <v>43</v>
       </c>
       <c r="B39" t="n">
-        <v>576</v>
+        <v>667</v>
       </c>
       <c r="C39" t="n">
         <v>575</v>
       </c>
       <c r="D39" t="n">
-        <v>537</v>
+        <v>556</v>
       </c>
       <c r="E39" t="n">
-        <v>592</v>
+        <v>616</v>
       </c>
       <c r="F39" t="n">
-        <v>607</v>
+        <v>619</v>
       </c>
       <c r="G39" t="n">
-        <v>597</v>
+        <v>544</v>
       </c>
       <c r="H39" t="n">
-        <v>661</v>
+        <v>567</v>
       </c>
       <c r="I39" t="n">
-        <v>599</v>
+        <v>583</v>
       </c>
       <c r="J39" t="n">
-        <v>535</v>
+        <v>574</v>
       </c>
       <c r="K39" t="n">
-        <v>616</v>
+        <v>643</v>
       </c>
       <c r="L39" t="n">
-        <v>589.5</v>
+        <v>594.4</v>
       </c>
     </row>
     <row r="40">
@@ -1915,37 +1915,37 @@
         <v>44</v>
       </c>
       <c r="B40" t="n">
-        <v>787</v>
+        <v>785</v>
       </c>
       <c r="C40" t="n">
-        <v>727</v>
+        <v>722</v>
       </c>
       <c r="D40" t="n">
-        <v>750</v>
+        <v>635</v>
       </c>
       <c r="E40" t="n">
-        <v>605</v>
+        <v>686</v>
       </c>
       <c r="F40" t="n">
-        <v>757</v>
+        <v>689</v>
       </c>
       <c r="G40" t="n">
-        <v>683</v>
+        <v>692</v>
       </c>
       <c r="H40" t="n">
-        <v>740</v>
+        <v>687</v>
       </c>
       <c r="I40" t="n">
-        <v>718</v>
+        <v>659</v>
       </c>
       <c r="J40" t="n">
-        <v>774</v>
+        <v>772</v>
       </c>
       <c r="K40" t="n">
-        <v>702</v>
+        <v>681</v>
       </c>
       <c r="L40" t="n">
-        <v>724.3</v>
+        <v>700.8</v>
       </c>
     </row>
     <row r="41">
@@ -1953,37 +1953,37 @@
         <v>45</v>
       </c>
       <c r="B41" t="n">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="C41" t="n">
-        <v>683</v>
+        <v>718</v>
       </c>
       <c r="D41" t="n">
-        <v>701</v>
+        <v>641</v>
       </c>
       <c r="E41" t="n">
-        <v>643</v>
+        <v>702</v>
       </c>
       <c r="F41" t="n">
-        <v>617</v>
+        <v>585</v>
       </c>
       <c r="G41" t="n">
-        <v>617</v>
+        <v>665</v>
       </c>
       <c r="H41" t="n">
-        <v>601</v>
+        <v>661</v>
       </c>
       <c r="I41" t="n">
-        <v>673</v>
+        <v>676</v>
       </c>
       <c r="J41" t="n">
-        <v>673</v>
+        <v>607</v>
       </c>
       <c r="K41" t="n">
-        <v>678</v>
+        <v>639</v>
       </c>
       <c r="L41" t="n">
-        <v>649.2</v>
+        <v>650.1</v>
       </c>
     </row>
     <row r="42">
@@ -1991,37 +1991,37 @@
         <v>46</v>
       </c>
       <c r="B42" t="n">
-        <v>627</v>
+        <v>649</v>
       </c>
       <c r="C42" t="n">
-        <v>615</v>
+        <v>608</v>
       </c>
       <c r="D42" t="n">
         <v>597</v>
       </c>
       <c r="E42" t="n">
-        <v>524</v>
+        <v>608</v>
       </c>
       <c r="F42" t="n">
-        <v>675</v>
+        <v>587</v>
       </c>
       <c r="G42" t="n">
-        <v>607</v>
+        <v>567</v>
       </c>
       <c r="H42" t="n">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="I42" t="n">
-        <v>648</v>
+        <v>616</v>
       </c>
       <c r="J42" t="n">
-        <v>654</v>
+        <v>696</v>
       </c>
       <c r="K42" t="n">
-        <v>710</v>
+        <v>570</v>
       </c>
       <c r="L42" t="n">
-        <v>625.5</v>
+        <v>609.7</v>
       </c>
     </row>
     <row r="43">
@@ -2029,37 +2029,37 @@
         <v>47</v>
       </c>
       <c r="B43" t="n">
-        <v>607</v>
+        <v>771</v>
       </c>
       <c r="C43" t="n">
-        <v>607</v>
+        <v>689</v>
       </c>
       <c r="D43" t="n">
-        <v>738</v>
+        <v>708</v>
       </c>
       <c r="E43" t="n">
-        <v>612</v>
+        <v>674</v>
       </c>
       <c r="F43" t="n">
-        <v>739</v>
+        <v>682</v>
       </c>
       <c r="G43" t="n">
-        <v>617</v>
+        <v>648</v>
       </c>
       <c r="H43" t="n">
-        <v>701</v>
+        <v>774</v>
       </c>
       <c r="I43" t="n">
-        <v>636</v>
+        <v>613</v>
       </c>
       <c r="J43" t="n">
-        <v>689</v>
+        <v>667</v>
       </c>
       <c r="K43" t="n">
-        <v>662</v>
+        <v>620</v>
       </c>
       <c r="L43" t="n">
-        <v>660.8</v>
+        <v>684.6</v>
       </c>
     </row>
     <row r="44">
@@ -2067,37 +2067,37 @@
         <v>48</v>
       </c>
       <c r="B44" t="n">
-        <v>712</v>
+        <v>678</v>
       </c>
       <c r="C44" t="n">
-        <v>676</v>
+        <v>694</v>
       </c>
       <c r="D44" t="n">
-        <v>736</v>
+        <v>696</v>
       </c>
       <c r="E44" t="n">
-        <v>726</v>
+        <v>783</v>
       </c>
       <c r="F44" t="n">
-        <v>605</v>
+        <v>694</v>
       </c>
       <c r="G44" t="n">
-        <v>749</v>
+        <v>788</v>
       </c>
       <c r="H44" t="n">
-        <v>768</v>
+        <v>688</v>
       </c>
       <c r="I44" t="n">
-        <v>808</v>
+        <v>739</v>
       </c>
       <c r="J44" t="n">
-        <v>685</v>
+        <v>774</v>
       </c>
       <c r="K44" t="n">
-        <v>751</v>
+        <v>766</v>
       </c>
       <c r="L44" t="n">
-        <v>721.6</v>
+        <v>730</v>
       </c>
     </row>
     <row r="45">
@@ -2105,37 +2105,37 @@
         <v>49</v>
       </c>
       <c r="B45" t="n">
-        <v>665</v>
+        <v>593</v>
       </c>
       <c r="C45" t="n">
+        <v>617</v>
+      </c>
+      <c r="D45" t="n">
+        <v>599</v>
+      </c>
+      <c r="E45" t="n">
         <v>626</v>
       </c>
-      <c r="D45" t="n">
-        <v>607</v>
-      </c>
-      <c r="E45" t="n">
-        <v>535</v>
-      </c>
       <c r="F45" t="n">
-        <v>614</v>
+        <v>662</v>
       </c>
       <c r="G45" t="n">
-        <v>570</v>
+        <v>637</v>
       </c>
       <c r="H45" t="n">
-        <v>585</v>
+        <v>596</v>
       </c>
       <c r="I45" t="n">
-        <v>589</v>
+        <v>650</v>
       </c>
       <c r="J45" t="n">
-        <v>596</v>
+        <v>600</v>
       </c>
       <c r="K45" t="n">
-        <v>576</v>
+        <v>606</v>
       </c>
       <c r="L45" t="n">
-        <v>596.3</v>
+        <v>618.6</v>
       </c>
     </row>
     <row r="46">
@@ -2143,37 +2143,37 @@
         <v>5</v>
       </c>
       <c r="B46" t="n">
-        <v>627</v>
+        <v>708</v>
       </c>
       <c r="C46" t="n">
-        <v>628</v>
+        <v>667</v>
       </c>
       <c r="D46" t="n">
-        <v>612</v>
+        <v>652</v>
       </c>
       <c r="E46" t="n">
-        <v>638</v>
+        <v>611</v>
       </c>
       <c r="F46" t="n">
-        <v>654</v>
+        <v>625</v>
       </c>
       <c r="G46" t="n">
-        <v>853</v>
+        <v>700</v>
       </c>
       <c r="H46" t="n">
-        <v>667</v>
+        <v>611</v>
       </c>
       <c r="I46" t="n">
-        <v>703</v>
+        <v>809</v>
       </c>
       <c r="J46" t="n">
-        <v>585</v>
+        <v>636</v>
       </c>
       <c r="K46" t="n">
-        <v>719</v>
+        <v>644</v>
       </c>
       <c r="L46" t="n">
-        <v>668.6</v>
+        <v>666.3</v>
       </c>
     </row>
     <row r="47">
@@ -2181,37 +2181,37 @@
         <v>50</v>
       </c>
       <c r="B47" t="n">
-        <v>789</v>
+        <v>683</v>
       </c>
       <c r="C47" t="n">
-        <v>835</v>
+        <v>722</v>
       </c>
       <c r="D47" t="n">
-        <v>775</v>
+        <v>763</v>
       </c>
       <c r="E47" t="n">
-        <v>592</v>
+        <v>806</v>
       </c>
       <c r="F47" t="n">
-        <v>723</v>
+        <v>619</v>
       </c>
       <c r="G47" t="n">
-        <v>775</v>
+        <v>735</v>
       </c>
       <c r="H47" t="n">
-        <v>694</v>
+        <v>666</v>
       </c>
       <c r="I47" t="n">
-        <v>820</v>
+        <v>714</v>
       </c>
       <c r="J47" t="n">
-        <v>797</v>
+        <v>788</v>
       </c>
       <c r="K47" t="n">
-        <v>656</v>
+        <v>782</v>
       </c>
       <c r="L47" t="n">
-        <v>745.6</v>
+        <v>727.8</v>
       </c>
     </row>
     <row r="48">
@@ -2219,37 +2219,37 @@
         <v>6</v>
       </c>
       <c r="B48" t="n">
-        <v>646</v>
+        <v>640</v>
       </c>
       <c r="C48" t="n">
-        <v>620</v>
+        <v>626</v>
       </c>
       <c r="D48" t="n">
-        <v>608</v>
+        <v>672</v>
       </c>
       <c r="E48" t="n">
-        <v>676</v>
+        <v>668</v>
       </c>
       <c r="F48" t="n">
-        <v>610</v>
+        <v>672</v>
       </c>
       <c r="G48" t="n">
-        <v>664</v>
+        <v>667</v>
       </c>
       <c r="H48" t="n">
-        <v>649</v>
+        <v>607</v>
       </c>
       <c r="I48" t="n">
-        <v>660</v>
+        <v>718</v>
       </c>
       <c r="J48" t="n">
-        <v>657</v>
+        <v>609</v>
       </c>
       <c r="K48" t="n">
-        <v>662</v>
+        <v>666</v>
       </c>
       <c r="L48" t="n">
-        <v>645.2</v>
+        <v>654.5</v>
       </c>
     </row>
     <row r="49">
@@ -2257,37 +2257,37 @@
         <v>7</v>
       </c>
       <c r="B49" t="n">
-        <v>790</v>
+        <v>773</v>
       </c>
       <c r="C49" t="n">
+        <v>852</v>
+      </c>
+      <c r="D49" t="n">
+        <v>807</v>
+      </c>
+      <c r="E49" t="n">
         <v>724</v>
-      </c>
-      <c r="D49" t="n">
-        <v>741</v>
-      </c>
-      <c r="E49" t="n">
-        <v>797</v>
       </c>
       <c r="F49" t="n">
         <v>740</v>
       </c>
       <c r="G49" t="n">
-        <v>687</v>
+        <v>754</v>
       </c>
       <c r="H49" t="n">
-        <v>823</v>
+        <v>782</v>
       </c>
       <c r="I49" t="n">
-        <v>811</v>
+        <v>726</v>
       </c>
       <c r="J49" t="n">
-        <v>739</v>
+        <v>805</v>
       </c>
       <c r="K49" t="n">
-        <v>827</v>
+        <v>768</v>
       </c>
       <c r="L49" t="n">
-        <v>767.9</v>
+        <v>773.1</v>
       </c>
     </row>
     <row r="50">
@@ -2295,37 +2295,37 @@
         <v>8</v>
       </c>
       <c r="B50" t="n">
-        <v>645</v>
+        <v>669</v>
       </c>
       <c r="C50" t="n">
-        <v>661</v>
+        <v>689</v>
       </c>
       <c r="D50" t="n">
-        <v>566</v>
+        <v>657</v>
       </c>
       <c r="E50" t="n">
-        <v>661</v>
+        <v>730</v>
       </c>
       <c r="F50" t="n">
-        <v>628</v>
+        <v>646</v>
       </c>
       <c r="G50" t="n">
-        <v>639</v>
+        <v>686</v>
       </c>
       <c r="H50" t="n">
-        <v>695</v>
+        <v>595</v>
       </c>
       <c r="I50" t="n">
-        <v>688</v>
+        <v>694</v>
       </c>
       <c r="J50" t="n">
-        <v>671</v>
+        <v>619</v>
       </c>
       <c r="K50" t="n">
-        <v>671</v>
+        <v>582</v>
       </c>
       <c r="L50" t="n">
-        <v>652.5</v>
+        <v>656.7</v>
       </c>
     </row>
     <row r="51">
@@ -2333,37 +2333,37 @@
         <v>9</v>
       </c>
       <c r="B51" t="n">
-        <v>725</v>
+        <v>732</v>
       </c>
       <c r="C51" t="n">
-        <v>664</v>
+        <v>687</v>
       </c>
       <c r="D51" t="n">
-        <v>749</v>
+        <v>686</v>
       </c>
       <c r="E51" t="n">
-        <v>665</v>
+        <v>645</v>
       </c>
       <c r="F51" t="n">
-        <v>671</v>
+        <v>654</v>
       </c>
       <c r="G51" t="n">
-        <v>596</v>
+        <v>653</v>
       </c>
       <c r="H51" t="n">
-        <v>642</v>
+        <v>699</v>
       </c>
       <c r="I51" t="n">
-        <v>700</v>
+        <v>666</v>
       </c>
       <c r="J51" t="n">
-        <v>681</v>
+        <v>723</v>
       </c>
       <c r="K51" t="n">
-        <v>623</v>
+        <v>676</v>
       </c>
       <c r="L51" t="n">
-        <v>671.6</v>
+        <v>682.1</v>
       </c>
     </row>
     <row r="52">
@@ -2373,37 +2373,37 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>692.54</v>
+        <v>683.28</v>
       </c>
       <c r="C52" t="n">
-        <v>688.64</v>
+        <v>689.76</v>
       </c>
       <c r="D52" t="n">
-        <v>679.26</v>
+        <v>676.74</v>
       </c>
       <c r="E52" t="n">
-        <v>675.42</v>
+        <v>688.46</v>
       </c>
       <c r="F52" t="n">
-        <v>683.1799999999999</v>
+        <v>666.52</v>
       </c>
       <c r="G52" t="n">
-        <v>676.3</v>
+        <v>691.92</v>
       </c>
       <c r="H52" t="n">
-        <v>685.66</v>
+        <v>681.5</v>
       </c>
       <c r="I52" t="n">
-        <v>696.34</v>
+        <v>682.8</v>
       </c>
       <c r="J52" t="n">
-        <v>685.22</v>
+        <v>681.42</v>
       </c>
       <c r="K52" t="n">
-        <v>691.42</v>
+        <v>682.74</v>
       </c>
       <c r="L52" t="n">
-        <v>685.398</v>
+        <v>682.5139999999998</v>
       </c>
     </row>
   </sheetData>
@@ -2462,37 +2462,37 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>4.177852630615234</v>
+        <v>6.017978429794312</v>
       </c>
       <c r="C2" t="n">
-        <v>3.549965143203735</v>
+        <v>4.61497974395752</v>
       </c>
       <c r="D2" t="n">
-        <v>3.844185352325439</v>
+        <v>3.945459604263306</v>
       </c>
       <c r="E2" t="n">
-        <v>4.687608003616333</v>
+        <v>4.508836269378662</v>
       </c>
       <c r="F2" t="n">
-        <v>4.108032941818237</v>
+        <v>4.324606895446777</v>
       </c>
       <c r="G2" t="n">
-        <v>3.929496765136719</v>
+        <v>4.098307847976685</v>
       </c>
       <c r="H2" t="n">
-        <v>4.368895053863525</v>
+        <v>4.463086366653442</v>
       </c>
       <c r="I2" t="n">
-        <v>4.200303077697754</v>
+        <v>4.213312387466431</v>
       </c>
       <c r="J2" t="n">
-        <v>3.819272994995117</v>
+        <v>4.418555974960327</v>
       </c>
       <c r="K2" t="n">
-        <v>4.610260725021362</v>
+        <v>4.508283138275146</v>
       </c>
       <c r="L2" t="n">
-        <v>4.129587268829345</v>
+        <v>4.511340665817261</v>
       </c>
     </row>
     <row r="3">
@@ -2500,37 +2500,37 @@
         <v>10</v>
       </c>
       <c r="B3" t="n">
-        <v>4.261149644851685</v>
+        <v>5.223129510879517</v>
       </c>
       <c r="C3" t="n">
-        <v>4.349018096923828</v>
+        <v>5.151026487350464</v>
       </c>
       <c r="D3" t="n">
-        <v>4.028733491897583</v>
+        <v>4.813965082168579</v>
       </c>
       <c r="E3" t="n">
-        <v>5.189796447753906</v>
+        <v>4.824663400650024</v>
       </c>
       <c r="F3" t="n">
-        <v>4.287062883377075</v>
+        <v>4.627513647079468</v>
       </c>
       <c r="G3" t="n">
-        <v>4.21026611328125</v>
+        <v>4.6858971118927</v>
       </c>
       <c r="H3" t="n">
-        <v>4.700521230697632</v>
+        <v>5.329923391342163</v>
       </c>
       <c r="I3" t="n">
-        <v>4.662636041641235</v>
+        <v>4.726592779159546</v>
       </c>
       <c r="J3" t="n">
-        <v>4.31351113319397</v>
+        <v>4.753752470016479</v>
       </c>
       <c r="K3" t="n">
-        <v>4.55191969871521</v>
+        <v>4.672863960266113</v>
       </c>
       <c r="L3" t="n">
-        <v>4.455461478233337</v>
+        <v>4.880932784080505</v>
       </c>
     </row>
     <row r="4">
@@ -2538,37 +2538,37 @@
         <v>11</v>
       </c>
       <c r="B4" t="n">
-        <v>4.813751697540283</v>
+        <v>5.198555469512939</v>
       </c>
       <c r="C4" t="n">
-        <v>4.741951942443848</v>
+        <v>4.911529302597046</v>
       </c>
       <c r="D4" t="n">
-        <v>4.226236343383789</v>
+        <v>4.73206090927124</v>
       </c>
       <c r="E4" t="n">
-        <v>5.187259912490845</v>
+        <v>4.859374046325684</v>
       </c>
       <c r="F4" t="n">
-        <v>4.353912830352783</v>
+        <v>4.633145093917847</v>
       </c>
       <c r="G4" t="n">
-        <v>4.160936117172241</v>
+        <v>4.787497282028198</v>
       </c>
       <c r="H4" t="n">
-        <v>4.288553476333618</v>
+        <v>5.083889245986938</v>
       </c>
       <c r="I4" t="n">
-        <v>4.281587362289429</v>
+        <v>4.905035734176636</v>
       </c>
       <c r="J4" t="n">
-        <v>4.339444160461426</v>
+        <v>4.816598176956177</v>
       </c>
       <c r="K4" t="n">
-        <v>4.686562776565552</v>
+        <v>4.894519567489624</v>
       </c>
       <c r="L4" t="n">
-        <v>4.508019661903381</v>
+        <v>4.882220482826233</v>
       </c>
     </row>
     <row r="5">
@@ -2576,37 +2576,37 @@
         <v>12</v>
       </c>
       <c r="B5" t="n">
-        <v>5.397290945053101</v>
+        <v>5.972520351409912</v>
       </c>
       <c r="C5" t="n">
-        <v>4.818943977355957</v>
+        <v>5.182342767715454</v>
       </c>
       <c r="D5" t="n">
-        <v>4.793524980545044</v>
+        <v>5.248969554901123</v>
       </c>
       <c r="E5" t="n">
-        <v>4.638959169387817</v>
+        <v>5.017710208892822</v>
       </c>
       <c r="F5" t="n">
-        <v>4.941647291183472</v>
+        <v>5.030667066574097</v>
       </c>
       <c r="G5" t="n">
-        <v>4.915699005126953</v>
+        <v>5.078776836395264</v>
       </c>
       <c r="H5" t="n">
-        <v>4.448944807052612</v>
+        <v>5.167298555374146</v>
       </c>
       <c r="I5" t="n">
-        <v>5.662270784378052</v>
+        <v>5.276777505874634</v>
       </c>
       <c r="J5" t="n">
-        <v>4.970069885253906</v>
+        <v>5.022309064865112</v>
       </c>
       <c r="K5" t="n">
-        <v>5.096231460571289</v>
+        <v>4.924254179000854</v>
       </c>
       <c r="L5" t="n">
-        <v>4.96835823059082</v>
+        <v>5.192162609100341</v>
       </c>
     </row>
     <row r="6">
@@ -2614,37 +2614,37 @@
         <v>13</v>
       </c>
       <c r="B6" t="n">
-        <v>3.696888446807861</v>
+        <v>3.685654401779175</v>
       </c>
       <c r="C6" t="n">
-        <v>3.86393141746521</v>
+        <v>4.095790386199951</v>
       </c>
       <c r="D6" t="n">
-        <v>3.804103136062622</v>
+        <v>3.905504465103149</v>
       </c>
       <c r="E6" t="n">
-        <v>3.690902948379517</v>
+        <v>4.047325611114502</v>
       </c>
       <c r="F6" t="n">
-        <v>3.571205139160156</v>
+        <v>3.952640771865845</v>
       </c>
       <c r="G6" t="n">
-        <v>3.665990829467773</v>
+        <v>3.986396551132202</v>
       </c>
       <c r="H6" t="n">
-        <v>3.462481498718262</v>
+        <v>4.05562686920166</v>
       </c>
       <c r="I6" t="n">
-        <v>3.722807884216309</v>
+        <v>4.146556377410889</v>
       </c>
       <c r="J6" t="n">
-        <v>3.962192296981812</v>
+        <v>4.04841947555542</v>
       </c>
       <c r="K6" t="n">
-        <v>3.86046028137207</v>
+        <v>4.043335199356079</v>
       </c>
       <c r="L6" t="n">
-        <v>3.730096387863159</v>
+        <v>3.996725010871887</v>
       </c>
     </row>
     <row r="7">
@@ -2652,37 +2652,37 @@
         <v>14</v>
       </c>
       <c r="B7" t="n">
-        <v>4.272399663925171</v>
+        <v>5.333869934082031</v>
       </c>
       <c r="C7" t="n">
-        <v>4.522751569747925</v>
+        <v>5.171947002410889</v>
       </c>
       <c r="D7" t="n">
-        <v>4.602022409439087</v>
+        <v>4.924611806869507</v>
       </c>
       <c r="E7" t="n">
-        <v>4.870861053466797</v>
+        <v>5.752060174942017</v>
       </c>
       <c r="F7" t="n">
-        <v>4.408524990081787</v>
+        <v>5.120075941085815</v>
       </c>
       <c r="G7" t="n">
-        <v>4.807496070861816</v>
+        <v>4.968789100646973</v>
       </c>
       <c r="H7" t="n">
-        <v>4.263133525848389</v>
+        <v>5.347944021224976</v>
       </c>
       <c r="I7" t="n">
-        <v>4.824761629104614</v>
+        <v>5.714407205581665</v>
       </c>
       <c r="J7" t="n">
-        <v>6.152417898178101</v>
+        <v>5.030185699462891</v>
       </c>
       <c r="K7" t="n">
-        <v>4.49607515335083</v>
+        <v>4.965752840042114</v>
       </c>
       <c r="L7" t="n">
-        <v>4.722044396400451</v>
+        <v>5.232964372634887</v>
       </c>
     </row>
     <row r="8">
@@ -2690,37 +2690,37 @@
         <v>15</v>
       </c>
       <c r="B8" t="n">
-        <v>3.707066297531128</v>
+        <v>4.21144700050354</v>
       </c>
       <c r="C8" t="n">
-        <v>3.688592910766602</v>
+        <v>4.060970067977905</v>
       </c>
       <c r="D8" t="n">
-        <v>3.559941530227661</v>
+        <v>4.379838943481445</v>
       </c>
       <c r="E8" t="n">
-        <v>3.988826274871826</v>
+        <v>4.090311288833618</v>
       </c>
       <c r="F8" t="n">
-        <v>3.772948265075684</v>
+        <v>4.377300977706909</v>
       </c>
       <c r="G8" t="n">
-        <v>4.025736570358276</v>
+        <v>4.347055435180664</v>
       </c>
       <c r="H8" t="n">
-        <v>3.779373645782471</v>
+        <v>4.33685564994812</v>
       </c>
       <c r="I8" t="n">
-        <v>4.124978303909302</v>
+        <v>4.463664293289185</v>
       </c>
       <c r="J8" t="n">
-        <v>3.766398429870605</v>
+        <v>4.659417629241943</v>
       </c>
       <c r="K8" t="n">
-        <v>4.373853206634521</v>
+        <v>4.216033935546875</v>
       </c>
       <c r="L8" t="n">
-        <v>3.878771543502808</v>
+        <v>4.314289522171021</v>
       </c>
     </row>
     <row r="9">
@@ -2728,37 +2728,37 @@
         <v>16</v>
       </c>
       <c r="B9" t="n">
-        <v>3.645750522613525</v>
+        <v>4.212091684341431</v>
       </c>
       <c r="C9" t="n">
-        <v>3.623768329620361</v>
+        <v>4.348361015319824</v>
       </c>
       <c r="D9" t="n">
-        <v>4.01676869392395</v>
+        <v>4.157585620880127</v>
       </c>
       <c r="E9" t="n">
-        <v>3.384379148483276</v>
+        <v>4.770412921905518</v>
       </c>
       <c r="F9" t="n">
-        <v>3.512545347213745</v>
+        <v>4.084722280502319</v>
       </c>
       <c r="G9" t="n">
-        <v>3.63474702835083</v>
+        <v>4.143538236618042</v>
       </c>
       <c r="H9" t="n">
-        <v>3.626289367675781</v>
+        <v>3.884553194046021</v>
       </c>
       <c r="I9" t="n">
-        <v>3.680602788925171</v>
+        <v>4.200825452804565</v>
       </c>
       <c r="J9" t="n">
-        <v>3.648225069046021</v>
+        <v>4.538375616073608</v>
       </c>
       <c r="K9" t="n">
-        <v>3.577369213104248</v>
+        <v>3.75680136680603</v>
       </c>
       <c r="L9" t="n">
-        <v>3.635044550895691</v>
+        <v>4.209726738929748</v>
       </c>
     </row>
     <row r="10">
@@ -2766,37 +2766,37 @@
         <v>17</v>
       </c>
       <c r="B10" t="n">
-        <v>4.43022894859314</v>
+        <v>5.118250608444214</v>
       </c>
       <c r="C10" t="n">
-        <v>5.356836557388306</v>
+        <v>5.497452259063721</v>
       </c>
       <c r="D10" t="n">
-        <v>4.603289604187012</v>
+        <v>5.087492704391479</v>
       </c>
       <c r="E10" t="n">
-        <v>4.538959980010986</v>
+        <v>5.261510848999023</v>
       </c>
       <c r="F10" t="n">
-        <v>4.241191148757935</v>
+        <v>5.265861988067627</v>
       </c>
       <c r="G10" t="n">
-        <v>4.996283292770386</v>
+        <v>5.417868137359619</v>
       </c>
       <c r="H10" t="n">
-        <v>4.687606811523438</v>
+        <v>5.331702470779419</v>
       </c>
       <c r="I10" t="n">
-        <v>4.975347995758057</v>
+        <v>5.659779787063599</v>
       </c>
       <c r="J10" t="n">
-        <v>4.87158203125</v>
+        <v>4.882625579833984</v>
       </c>
       <c r="K10" t="n">
-        <v>4.707507133483887</v>
+        <v>5.960528373718262</v>
       </c>
       <c r="L10" t="n">
-        <v>4.740883350372314</v>
+        <v>5.348307275772095</v>
       </c>
     </row>
     <row r="11">
@@ -2804,37 +2804,37 @@
         <v>18</v>
       </c>
       <c r="B11" t="n">
-        <v>4.043208122253418</v>
+        <v>4.717704057693481</v>
       </c>
       <c r="C11" t="n">
-        <v>4.077590465545654</v>
+        <v>4.912238836288452</v>
       </c>
       <c r="D11" t="n">
-        <v>3.800311803817749</v>
+        <v>4.896513223648071</v>
       </c>
       <c r="E11" t="n">
-        <v>4.011781692504883</v>
+        <v>5.622297048568726</v>
       </c>
       <c r="F11" t="n">
-        <v>4.104029655456543</v>
+        <v>4.751218557357788</v>
       </c>
       <c r="G11" t="n">
-        <v>4.028739452362061</v>
+        <v>5.765851259231567</v>
       </c>
       <c r="H11" t="n">
-        <v>4.038218975067139</v>
+        <v>5.188984155654907</v>
       </c>
       <c r="I11" t="n">
-        <v>4.14693808555603</v>
+        <v>5.924156427383423</v>
       </c>
       <c r="J11" t="n">
-        <v>4.142937898635864</v>
+        <v>5.791847944259644</v>
       </c>
       <c r="K11" t="n">
-        <v>4.079120397567749</v>
+        <v>4.496797561645508</v>
       </c>
       <c r="L11" t="n">
-        <v>4.047287654876709</v>
+        <v>5.206760907173157</v>
       </c>
     </row>
     <row r="12">
@@ -2842,37 +2842,37 @@
         <v>19</v>
       </c>
       <c r="B12" t="n">
-        <v>3.784382104873657</v>
+        <v>4.581225395202637</v>
       </c>
       <c r="C12" t="n">
-        <v>3.991882801055908</v>
+        <v>4.324319362640381</v>
       </c>
       <c r="D12" t="n">
-        <v>3.775879621505737</v>
+        <v>4.191845417022705</v>
       </c>
       <c r="E12" t="n">
-        <v>3.879639148712158</v>
+        <v>4.559959888458252</v>
       </c>
       <c r="F12" t="n">
-        <v>3.675166130065918</v>
+        <v>5.261037826538086</v>
       </c>
       <c r="G12" t="n">
-        <v>3.777890682220459</v>
+        <v>4.346704721450806</v>
       </c>
       <c r="H12" t="n">
-        <v>3.689117670059204</v>
+        <v>4.315936326980591</v>
       </c>
       <c r="I12" t="n">
-        <v>3.788366556167603</v>
+        <v>3.904540777206421</v>
       </c>
       <c r="J12" t="n">
-        <v>3.688127756118774</v>
+        <v>4.137884140014648</v>
       </c>
       <c r="K12" t="n">
-        <v>3.782857418060303</v>
+        <v>4.109246730804443</v>
       </c>
       <c r="L12" t="n">
-        <v>3.783330988883972</v>
+        <v>4.373270058631897</v>
       </c>
     </row>
     <row r="13">
@@ -2880,37 +2880,37 @@
         <v>2</v>
       </c>
       <c r="B13" t="n">
-        <v>3.657200574874878</v>
+        <v>4.184435367584229</v>
       </c>
       <c r="C13" t="n">
-        <v>3.792341709136963</v>
+        <v>4.025899410247803</v>
       </c>
       <c r="D13" t="n">
-        <v>3.405335903167725</v>
+        <v>4.872018098831177</v>
       </c>
       <c r="E13" t="n">
-        <v>3.772890567779541</v>
+        <v>4.651235580444336</v>
       </c>
       <c r="F13" t="n">
-        <v>3.683109521865845</v>
+        <v>4.583001136779785</v>
       </c>
       <c r="G13" t="n">
-        <v>3.481630563735962</v>
+        <v>4.686460971832275</v>
       </c>
       <c r="H13" t="n">
-        <v>4.025752782821655</v>
+        <v>4.699963569641113</v>
       </c>
       <c r="I13" t="n">
-        <v>3.801313400268555</v>
+        <v>4.785285949707031</v>
       </c>
       <c r="J13" t="n">
-        <v>3.436249494552612</v>
+        <v>4.534846067428589</v>
       </c>
       <c r="K13" t="n">
-        <v>4.332459211349487</v>
+        <v>4.746291160583496</v>
       </c>
       <c r="L13" t="n">
-        <v>3.738828372955322</v>
+        <v>4.576943731307983</v>
       </c>
     </row>
     <row r="14">
@@ -2918,37 +2918,37 @@
         <v>20</v>
       </c>
       <c r="B14" t="n">
-        <v>3.856177568435669</v>
+        <v>5.116195678710938</v>
       </c>
       <c r="C14" t="n">
-        <v>3.805299758911133</v>
+        <v>4.714112043380737</v>
       </c>
       <c r="D14" t="n">
-        <v>3.948449611663818</v>
+        <v>4.380098342895508</v>
       </c>
       <c r="E14" t="n">
-        <v>3.843705415725708</v>
+        <v>4.459346294403076</v>
       </c>
       <c r="F14" t="n">
-        <v>3.81230092048645</v>
+        <v>4.035650968551636</v>
       </c>
       <c r="G14" t="n">
-        <v>3.970381259918213</v>
+        <v>4.342415809631348</v>
       </c>
       <c r="H14" t="n">
-        <v>4.348962783813477</v>
+        <v>4.484283924102783</v>
       </c>
       <c r="I14" t="n">
-        <v>3.880630970001221</v>
+        <v>5.071849822998047</v>
       </c>
       <c r="J14" t="n">
-        <v>4.081600666046143</v>
+        <v>4.62200665473938</v>
       </c>
       <c r="K14" t="n">
-        <v>3.893604755401611</v>
+        <v>4.554157257080078</v>
       </c>
       <c r="L14" t="n">
-        <v>3.944111371040344</v>
+        <v>4.578011679649353</v>
       </c>
     </row>
     <row r="15">
@@ -2956,37 +2956,37 @@
         <v>21</v>
       </c>
       <c r="B15" t="n">
-        <v>4.234719038009644</v>
+        <v>4.996063709259033</v>
       </c>
       <c r="C15" t="n">
-        <v>4.572863817214966</v>
+        <v>4.822835445404053</v>
       </c>
       <c r="D15" t="n">
-        <v>4.714498519897461</v>
+        <v>4.760306119918823</v>
       </c>
       <c r="E15" t="n">
-        <v>4.261661767959595</v>
+        <v>4.654022693634033</v>
       </c>
       <c r="F15" t="n">
-        <v>4.408773899078369</v>
+        <v>5.037844896316528</v>
       </c>
       <c r="G15" t="n">
-        <v>4.229212045669556</v>
+        <v>4.606796264648438</v>
       </c>
       <c r="H15" t="n">
-        <v>4.203293561935425</v>
+        <v>4.873852968215942</v>
       </c>
       <c r="I15" t="n">
-        <v>3.884595155715942</v>
+        <v>4.801549196243286</v>
       </c>
       <c r="J15" t="n">
-        <v>4.762355804443359</v>
+        <v>4.997769832611084</v>
       </c>
       <c r="K15" t="n">
-        <v>4.383852958679199</v>
+        <v>4.564243316650391</v>
       </c>
       <c r="L15" t="n">
-        <v>4.365582656860352</v>
+        <v>4.811528444290161</v>
       </c>
     </row>
     <row r="16">
@@ -2994,37 +2994,37 @@
         <v>22</v>
       </c>
       <c r="B16" t="n">
-        <v>3.81029748916626</v>
+        <v>4.343834400177002</v>
       </c>
       <c r="C16" t="n">
-        <v>3.881613492965698</v>
+        <v>4.044191122055054</v>
       </c>
       <c r="D16" t="n">
-        <v>3.963391065597534</v>
+        <v>4.33702826499939</v>
       </c>
       <c r="E16" t="n">
-        <v>3.991858720779419</v>
+        <v>4.402175426483154</v>
       </c>
       <c r="F16" t="n">
-        <v>4.07016134262085</v>
+        <v>4.422247409820557</v>
       </c>
       <c r="G16" t="n">
-        <v>4.301536798477173</v>
+        <v>4.373315572738647</v>
       </c>
       <c r="H16" t="n">
-        <v>4.223254442214966</v>
+        <v>4.472670793533325</v>
       </c>
       <c r="I16" t="n">
-        <v>4.010757446289062</v>
+        <v>4.329374074935913</v>
       </c>
       <c r="J16" t="n">
-        <v>3.861156940460205</v>
+        <v>4.569016933441162</v>
       </c>
       <c r="K16" t="n">
-        <v>3.72600793838501</v>
+        <v>4.905507564544678</v>
       </c>
       <c r="L16" t="n">
-        <v>3.984003567695618</v>
+        <v>4.419936156272888</v>
       </c>
     </row>
     <row r="17">
@@ -3032,37 +3032,37 @@
         <v>23</v>
       </c>
       <c r="B17" t="n">
-        <v>4.095067024230957</v>
+        <v>4.669552803039551</v>
       </c>
       <c r="C17" t="n">
-        <v>4.384834289550781</v>
+        <v>4.766531229019165</v>
       </c>
       <c r="D17" t="n">
-        <v>4.171411275863647</v>
+        <v>4.288493394851685</v>
       </c>
       <c r="E17" t="n">
-        <v>3.836214542388916</v>
+        <v>4.465937376022339</v>
       </c>
       <c r="F17" t="n">
-        <v>4.551925182342529</v>
+        <v>4.852150201797485</v>
       </c>
       <c r="G17" t="n">
-        <v>4.189331293106079</v>
+        <v>4.682625293731689</v>
       </c>
       <c r="H17" t="n">
-        <v>4.491083860397339</v>
+        <v>5.048940181732178</v>
       </c>
       <c r="I17" t="n">
-        <v>4.333453178405762</v>
+        <v>4.702539443969727</v>
       </c>
       <c r="J17" t="n">
-        <v>4.077118635177612</v>
+        <v>4.296202659606934</v>
       </c>
       <c r="K17" t="n">
-        <v>4.037711620330811</v>
+        <v>4.983230590820312</v>
       </c>
       <c r="L17" t="n">
-        <v>4.216815090179443</v>
+        <v>4.675620317459106</v>
       </c>
     </row>
     <row r="18">
@@ -3070,37 +3070,37 @@
         <v>24</v>
       </c>
       <c r="B18" t="n">
-        <v>3.897597551345825</v>
+        <v>4.054687261581421</v>
       </c>
       <c r="C18" t="n">
-        <v>3.570914506912231</v>
+        <v>3.850170373916626</v>
       </c>
       <c r="D18" t="n">
-        <v>3.883087873458862</v>
+        <v>4.024306058883667</v>
       </c>
       <c r="E18" t="n">
-        <v>3.445746898651123</v>
+        <v>4.034095287322998</v>
       </c>
       <c r="F18" t="n">
-        <v>3.476125240325928</v>
+        <v>4.255966424942017</v>
       </c>
       <c r="G18" t="n">
-        <v>3.476635217666626</v>
+        <v>3.952428579330444</v>
       </c>
       <c r="H18" t="n">
-        <v>3.425297975540161</v>
+        <v>4.123212337493896</v>
       </c>
       <c r="I18" t="n">
-        <v>3.598822116851807</v>
+        <v>3.990156888961792</v>
       </c>
       <c r="J18" t="n">
-        <v>3.420295476913452</v>
+        <v>3.970800399780273</v>
       </c>
       <c r="K18" t="n">
-        <v>3.664168119430542</v>
+        <v>4.126401901245117</v>
       </c>
       <c r="L18" t="n">
-        <v>3.585869097709656</v>
+        <v>4.038222551345825</v>
       </c>
     </row>
     <row r="19">
@@ -3108,37 +3108,37 @@
         <v>25</v>
       </c>
       <c r="B19" t="n">
-        <v>4.07712459564209</v>
+        <v>4.535120487213135</v>
       </c>
       <c r="C19" t="n">
-        <v>4.310513496398926</v>
+        <v>4.530094146728516</v>
       </c>
       <c r="D19" t="n">
-        <v>4.210267305374146</v>
+        <v>4.33407187461853</v>
       </c>
       <c r="E19" t="n">
-        <v>4.104536294937134</v>
+        <v>4.645212173461914</v>
       </c>
       <c r="F19" t="n">
-        <v>4.187355518341064</v>
+        <v>4.416842222213745</v>
       </c>
       <c r="G19" t="n">
-        <v>4.154413223266602</v>
+        <v>4.717966079711914</v>
       </c>
       <c r="H19" t="n">
-        <v>4.495084762573242</v>
+        <v>5.022185087203979</v>
       </c>
       <c r="I19" t="n">
-        <v>4.095829486846924</v>
+        <v>4.706346750259399</v>
       </c>
       <c r="J19" t="n">
-        <v>5.422029495239258</v>
+        <v>4.856710433959961</v>
       </c>
       <c r="K19" t="n">
-        <v>4.353909254074097</v>
+        <v>4.579324007034302</v>
       </c>
       <c r="L19" t="n">
-        <v>4.341106343269348</v>
+        <v>4.63438732624054</v>
       </c>
     </row>
     <row r="20">
@@ -3146,37 +3146,37 @@
         <v>26</v>
       </c>
       <c r="B20" t="n">
-        <v>3.735983371734619</v>
+        <v>4.325348138809204</v>
       </c>
       <c r="C20" t="n">
-        <v>3.890618801116943</v>
+        <v>4.345245122909546</v>
       </c>
       <c r="D20" t="n">
-        <v>3.982866525650024</v>
+        <v>4.276664018630981</v>
       </c>
       <c r="E20" t="n">
-        <v>4.032709836959839</v>
+        <v>5.1873459815979</v>
       </c>
       <c r="F20" t="n">
-        <v>4.650529861450195</v>
+        <v>4.406877040863037</v>
       </c>
       <c r="G20" t="n">
-        <v>3.943254232406616</v>
+        <v>4.569693565368652</v>
       </c>
       <c r="H20" t="n">
-        <v>3.900349140167236</v>
+        <v>4.433369159698486</v>
       </c>
       <c r="I20" t="n">
-        <v>4.08586597442627</v>
+        <v>4.637408971786499</v>
       </c>
       <c r="J20" t="n">
-        <v>3.942256689071655</v>
+        <v>4.445259809494019</v>
       </c>
       <c r="K20" t="n">
-        <v>4.629448890686035</v>
+        <v>4.529876708984375</v>
       </c>
       <c r="L20" t="n">
-        <v>4.079388332366944</v>
+        <v>4.51570885181427</v>
       </c>
     </row>
     <row r="21">
@@ -3184,37 +3184,37 @@
         <v>27</v>
       </c>
       <c r="B21" t="n">
-        <v>4.207061529159546</v>
+        <v>4.978386878967285</v>
       </c>
       <c r="C21" t="n">
-        <v>3.953238487243652</v>
+        <v>4.223031044006348</v>
       </c>
       <c r="D21" t="n">
-        <v>4.054947137832642</v>
+        <v>4.263303756713867</v>
       </c>
       <c r="E21" t="n">
-        <v>3.979401350021362</v>
+        <v>4.695528984069824</v>
       </c>
       <c r="F21" t="n">
-        <v>4.092100858688354</v>
+        <v>4.792427062988281</v>
       </c>
       <c r="G21" t="n">
-        <v>4.134980440139771</v>
+        <v>4.637592315673828</v>
       </c>
       <c r="H21" t="n">
-        <v>4.226226329803467</v>
+        <v>4.512744665145874</v>
       </c>
       <c r="I21" t="n">
-        <v>4.06516432762146</v>
+        <v>4.449860811233521</v>
       </c>
       <c r="J21" t="n">
-        <v>4.097063302993774</v>
+        <v>4.560476303100586</v>
       </c>
       <c r="K21" t="n">
-        <v>4.014778137207031</v>
+        <v>4.623699903488159</v>
       </c>
       <c r="L21" t="n">
-        <v>4.082496190071106</v>
+        <v>4.573705172538757</v>
       </c>
     </row>
     <row r="22">
@@ -3222,37 +3222,37 @@
         <v>28</v>
       </c>
       <c r="B22" t="n">
-        <v>3.825297355651855</v>
+        <v>4.495532035827637</v>
       </c>
       <c r="C22" t="n">
-        <v>3.995828866958618</v>
+        <v>4.308562040328979</v>
       </c>
       <c r="D22" t="n">
-        <v>3.885615587234497</v>
+        <v>4.314157009124756</v>
       </c>
       <c r="E22" t="n">
-        <v>3.812288761138916</v>
+        <v>4.486611366271973</v>
       </c>
       <c r="F22" t="n">
-        <v>3.773879528045654</v>
+        <v>4.529254913330078</v>
       </c>
       <c r="G22" t="n">
-        <v>4.077143907546997</v>
+        <v>4.247339248657227</v>
       </c>
       <c r="H22" t="n">
-        <v>3.84320330619812</v>
+        <v>4.554064750671387</v>
       </c>
       <c r="I22" t="n">
-        <v>4.177396297454834</v>
+        <v>4.29632306098938</v>
       </c>
       <c r="J22" t="n">
-        <v>3.886602401733398</v>
+        <v>4.715155601501465</v>
       </c>
       <c r="K22" t="n">
-        <v>3.928489923477173</v>
+        <v>4.656383752822876</v>
       </c>
       <c r="L22" t="n">
-        <v>3.920574593544006</v>
+        <v>4.460338377952576</v>
       </c>
     </row>
     <row r="23">
@@ -3260,37 +3260,37 @@
         <v>29</v>
       </c>
       <c r="B23" t="n">
-        <v>4.64873743057251</v>
+        <v>4.710771799087524</v>
       </c>
       <c r="C23" t="n">
-        <v>4.764360189437866</v>
+        <v>4.559215068817139</v>
       </c>
       <c r="D23" t="n">
-        <v>4.129968881607056</v>
+        <v>5.113208532333374</v>
       </c>
       <c r="E23" t="n">
-        <v>4.158400058746338</v>
+        <v>4.214343547821045</v>
       </c>
       <c r="F23" t="n">
-        <v>3.732021331787109</v>
+        <v>4.636513948440552</v>
       </c>
       <c r="G23" t="n">
-        <v>3.911537170410156</v>
+        <v>4.436949491500854</v>
       </c>
       <c r="H23" t="n">
-        <v>4.959859609603882</v>
+        <v>4.927066802978516</v>
       </c>
       <c r="I23" t="n">
-        <v>4.025246381759644</v>
+        <v>4.59745717048645</v>
       </c>
       <c r="J23" t="n">
-        <v>4.023733377456665</v>
+        <v>4.222133159637451</v>
       </c>
       <c r="K23" t="n">
-        <v>4.043730497360229</v>
+        <v>4.361393451690674</v>
       </c>
       <c r="L23" t="n">
-        <v>4.239759492874145</v>
+        <v>4.577905297279358</v>
       </c>
     </row>
     <row r="24">
@@ -3298,37 +3298,37 @@
         <v>3</v>
       </c>
       <c r="B24" t="n">
-        <v>4.42670464515686</v>
+        <v>4.312762260437012</v>
       </c>
       <c r="C24" t="n">
-        <v>4.010785102844238</v>
+        <v>4.359442710876465</v>
       </c>
       <c r="D24" t="n">
-        <v>3.67514443397522</v>
+        <v>4.347736835479736</v>
       </c>
       <c r="E24" t="n">
-        <v>3.719025135040283</v>
+        <v>5.454989910125732</v>
       </c>
       <c r="F24" t="n">
-        <v>4.36290454864502</v>
+        <v>4.647489547729492</v>
       </c>
       <c r="G24" t="n">
-        <v>4.289068698883057</v>
+        <v>4.407234907150269</v>
       </c>
       <c r="H24" t="n">
-        <v>3.743477582931519</v>
+        <v>4.183887481689453</v>
       </c>
       <c r="I24" t="n">
-        <v>3.826258897781372</v>
+        <v>5.136475324630737</v>
       </c>
       <c r="J24" t="n">
-        <v>4.265632152557373</v>
+        <v>4.684539794921875</v>
       </c>
       <c r="K24" t="n">
-        <v>3.850189924240112</v>
+        <v>4.702594041824341</v>
       </c>
       <c r="L24" t="n">
-        <v>4.016919112205505</v>
+        <v>4.623715281486511</v>
       </c>
     </row>
     <row r="25">
@@ -3336,37 +3336,37 @@
         <v>30</v>
       </c>
       <c r="B25" t="n">
-        <v>3.55942964553833</v>
+        <v>4.029758214950562</v>
       </c>
       <c r="C25" t="n">
-        <v>3.51306939125061</v>
+        <v>3.818857908248901</v>
       </c>
       <c r="D25" t="n">
-        <v>3.469164133071899</v>
+        <v>3.846673965454102</v>
       </c>
       <c r="E25" t="n">
-        <v>3.382370471954346</v>
+        <v>4.185350179672241</v>
       </c>
       <c r="F25" t="n">
-        <v>3.546455860137939</v>
+        <v>3.970158576965332</v>
       </c>
       <c r="G25" t="n">
-        <v>4.034805059432983</v>
+        <v>3.845790386199951</v>
       </c>
       <c r="H25" t="n">
-        <v>3.804304361343384</v>
+        <v>4.091735363006592</v>
       </c>
       <c r="I25" t="n">
-        <v>3.43276309967041</v>
+        <v>3.988524913787842</v>
       </c>
       <c r="J25" t="n">
-        <v>3.690601348876953</v>
+        <v>4.015499830245972</v>
       </c>
       <c r="K25" t="n">
-        <v>3.66217827796936</v>
+        <v>3.880138397216797</v>
       </c>
       <c r="L25" t="n">
-        <v>3.609514164924621</v>
+        <v>3.967248773574829</v>
       </c>
     </row>
     <row r="26">
@@ -3374,37 +3374,37 @@
         <v>31</v>
       </c>
       <c r="B26" t="n">
-        <v>4.299562692642212</v>
+        <v>4.693914175033569</v>
       </c>
       <c r="C26" t="n">
-        <v>4.259168148040771</v>
+        <v>4.680521011352539</v>
       </c>
       <c r="D26" t="n">
-        <v>4.230711936950684</v>
+        <v>4.608389854431152</v>
       </c>
       <c r="E26" t="n">
-        <v>4.776321887969971</v>
+        <v>4.682122230529785</v>
       </c>
       <c r="F26" t="n">
-        <v>4.180345773696899</v>
+        <v>4.756670713424683</v>
       </c>
       <c r="G26" t="n">
-        <v>4.233219385147095</v>
+        <v>4.772306442260742</v>
       </c>
       <c r="H26" t="n">
-        <v>4.169409275054932</v>
+        <v>4.636661767959595</v>
       </c>
       <c r="I26" t="n">
-        <v>4.884096145629883</v>
+        <v>4.721505403518677</v>
       </c>
       <c r="J26" t="n">
-        <v>4.17485785484314</v>
+        <v>4.878393888473511</v>
       </c>
       <c r="K26" t="n">
-        <v>4.50007963180542</v>
+        <v>5.020458221435547</v>
       </c>
       <c r="L26" t="n">
-        <v>4.370777273178101</v>
+        <v>4.74509437084198</v>
       </c>
     </row>
     <row r="27">
@@ -3412,37 +3412,37 @@
         <v>32</v>
       </c>
       <c r="B27" t="n">
-        <v>5.058635473251343</v>
+        <v>5.165977716445923</v>
       </c>
       <c r="C27" t="n">
-        <v>4.302016735076904</v>
+        <v>5.388570547103882</v>
       </c>
       <c r="D27" t="n">
-        <v>4.530457019805908</v>
+        <v>5.643357276916504</v>
       </c>
       <c r="E27" t="n">
-        <v>4.642164945602417</v>
+        <v>5.050978183746338</v>
       </c>
       <c r="F27" t="n">
-        <v>4.502043962478638</v>
+        <v>5.568523168563843</v>
       </c>
       <c r="G27" t="n">
-        <v>4.713501453399658</v>
+        <v>6.447356224060059</v>
       </c>
       <c r="H27" t="n">
-        <v>4.342438697814941</v>
+        <v>5.25446629524231</v>
       </c>
       <c r="I27" t="n">
-        <v>4.651053428649902</v>
+        <v>5.004953384399414</v>
       </c>
       <c r="J27" t="n">
-        <v>4.188395261764526</v>
+        <v>5.057630062103271</v>
       </c>
       <c r="K27" t="n">
-        <v>4.334964513778687</v>
+        <v>4.853221893310547</v>
       </c>
       <c r="L27" t="n">
-        <v>4.526567149162292</v>
+        <v>5.343503475189209</v>
       </c>
     </row>
     <row r="28">
@@ -3450,37 +3450,37 @@
         <v>33</v>
       </c>
       <c r="B28" t="n">
-        <v>3.871133804321289</v>
+        <v>4.390253067016602</v>
       </c>
       <c r="C28" t="n">
-        <v>3.831257343292236</v>
+        <v>4.521586179733276</v>
       </c>
       <c r="D28" t="n">
-        <v>3.952926397323608</v>
+        <v>4.459715604782104</v>
       </c>
       <c r="E28" t="n">
-        <v>4.045700073242188</v>
+        <v>4.453326940536499</v>
       </c>
       <c r="F28" t="n">
-        <v>4.205297470092773</v>
+        <v>4.127554655075073</v>
       </c>
       <c r="G28" t="n">
-        <v>3.781367301940918</v>
+        <v>4.254163265228271</v>
       </c>
       <c r="H28" t="n">
-        <v>3.925507307052612</v>
+        <v>4.320319890975952</v>
       </c>
       <c r="I28" t="n">
-        <v>3.892584562301636</v>
+        <v>4.400323152542114</v>
       </c>
       <c r="J28" t="n">
-        <v>4.051685810089111</v>
+        <v>4.623688459396362</v>
       </c>
       <c r="K28" t="n">
-        <v>4.037220239639282</v>
+        <v>4.343511819839478</v>
       </c>
       <c r="L28" t="n">
-        <v>3.959468030929565</v>
+        <v>4.389444303512573</v>
       </c>
     </row>
     <row r="29">
@@ -3488,37 +3488,37 @@
         <v>34</v>
       </c>
       <c r="B29" t="n">
-        <v>3.822175264358521</v>
+        <v>4.623473167419434</v>
       </c>
       <c r="C29" t="n">
-        <v>4.550667524337769</v>
+        <v>4.399313449859619</v>
       </c>
       <c r="D29" t="n">
-        <v>3.974655866622925</v>
+        <v>4.615944385528564</v>
       </c>
       <c r="E29" t="n">
-        <v>4.06342339515686</v>
+        <v>4.289638996124268</v>
       </c>
       <c r="F29" t="n">
-        <v>4.143223524093628</v>
+        <v>4.949179172515869</v>
       </c>
       <c r="G29" t="n">
-        <v>4.152682781219482</v>
+        <v>4.603907585144043</v>
       </c>
       <c r="H29" t="n">
-        <v>4.50396466255188</v>
+        <v>4.56199836730957</v>
       </c>
       <c r="I29" t="n">
-        <v>4.113041639328003</v>
+        <v>4.567723989486694</v>
       </c>
       <c r="J29" t="n">
-        <v>4.156415224075317</v>
+        <v>4.554286479949951</v>
       </c>
       <c r="K29" t="n">
-        <v>4.18383002281189</v>
+        <v>5.145598411560059</v>
       </c>
       <c r="L29" t="n">
-        <v>4.166407990455627</v>
+        <v>4.631106400489807</v>
       </c>
     </row>
     <row r="30">
@@ -3526,37 +3526,37 @@
         <v>35</v>
       </c>
       <c r="B30" t="n">
-        <v>3.771387577056885</v>
+        <v>4.355292320251465</v>
       </c>
       <c r="C30" t="n">
-        <v>4.183340072631836</v>
+        <v>4.392023801803589</v>
       </c>
       <c r="D30" t="n">
-        <v>3.7579345703125</v>
+        <v>4.101363658905029</v>
       </c>
       <c r="E30" t="n">
-        <v>4.098071098327637</v>
+        <v>4.103568315505981</v>
       </c>
       <c r="F30" t="n">
-        <v>3.870660305023193</v>
+        <v>4.360059499740601</v>
       </c>
       <c r="G30" t="n">
-        <v>3.675621032714844</v>
+        <v>4.183858871459961</v>
       </c>
       <c r="H30" t="n">
-        <v>3.791350603103638</v>
+        <v>4.549230337142944</v>
       </c>
       <c r="I30" t="n">
-        <v>3.992829322814941</v>
+        <v>4.629773855209351</v>
       </c>
       <c r="J30" t="n">
-        <v>4.334434509277344</v>
+        <v>4.486184120178223</v>
       </c>
       <c r="K30" t="n">
-        <v>4.053184032440186</v>
+        <v>4.192635059356689</v>
       </c>
       <c r="L30" t="n">
-        <v>3.9528813123703</v>
+        <v>4.335398983955383</v>
       </c>
     </row>
     <row r="31">
@@ -3564,37 +3564,37 @@
         <v>36</v>
       </c>
       <c r="B31" t="n">
-        <v>3.738959550857544</v>
+        <v>4.147396802902222</v>
       </c>
       <c r="C31" t="n">
-        <v>3.649687528610229</v>
+        <v>4.173153162002563</v>
       </c>
       <c r="D31" t="n">
-        <v>3.556957960128784</v>
+        <v>4.519944429397583</v>
       </c>
       <c r="E31" t="n">
-        <v>3.948450088500977</v>
+        <v>4.160478830337524</v>
       </c>
       <c r="F31" t="n">
-        <v>3.75345253944397</v>
+        <v>4.552569150924683</v>
       </c>
       <c r="G31" t="n">
-        <v>4.207318067550659</v>
+        <v>4.271530151367188</v>
       </c>
       <c r="H31" t="n">
-        <v>3.595321893692017</v>
+        <v>4.471185207366943</v>
       </c>
       <c r="I31" t="n">
-        <v>3.654213666915894</v>
+        <v>4.313578128814697</v>
       </c>
       <c r="J31" t="n">
-        <v>3.790358781814575</v>
+        <v>4.276134729385376</v>
       </c>
       <c r="K31" t="n">
-        <v>3.971386194229126</v>
+        <v>4.256580114364624</v>
       </c>
       <c r="L31" t="n">
-        <v>3.786610627174377</v>
+        <v>4.314255070686341</v>
       </c>
     </row>
     <row r="32">
@@ -3602,37 +3602,37 @@
         <v>37</v>
       </c>
       <c r="B32" t="n">
-        <v>3.851700782775879</v>
+        <v>4.152884721755981</v>
       </c>
       <c r="C32" t="n">
-        <v>4.093069791793823</v>
+        <v>4.581707000732422</v>
       </c>
       <c r="D32" t="n">
-        <v>4.409777402877808</v>
+        <v>4.046021938323975</v>
       </c>
       <c r="E32" t="n">
-        <v>3.68060040473938</v>
+        <v>4.441943883895874</v>
       </c>
       <c r="F32" t="n">
-        <v>4.105031490325928</v>
+        <v>4.25053071975708</v>
       </c>
       <c r="G32" t="n">
-        <v>3.898601531982422</v>
+        <v>4.653611898422241</v>
       </c>
       <c r="H32" t="n">
-        <v>4.035723686218262</v>
+        <v>4.161071062088013</v>
       </c>
       <c r="I32" t="n">
-        <v>3.770409822463989</v>
+        <v>3.958738327026367</v>
       </c>
       <c r="J32" t="n">
-        <v>4.117048740386963</v>
+        <v>3.993790864944458</v>
       </c>
       <c r="K32" t="n">
-        <v>3.801331996917725</v>
+        <v>4.766749382019043</v>
       </c>
       <c r="L32" t="n">
-        <v>3.976329565048218</v>
+        <v>4.300704979896546</v>
       </c>
     </row>
     <row r="33">
@@ -3640,37 +3640,37 @@
         <v>38</v>
       </c>
       <c r="B33" t="n">
-        <v>3.965916872024536</v>
+        <v>4.499316215515137</v>
       </c>
       <c r="C33" t="n">
-        <v>4.374346494674683</v>
+        <v>5.115722417831421</v>
       </c>
       <c r="D33" t="n">
-        <v>4.562402486801147</v>
+        <v>5.011537313461304</v>
       </c>
       <c r="E33" t="n">
-        <v>3.997806310653687</v>
+        <v>4.903127193450928</v>
       </c>
       <c r="F33" t="n">
-        <v>4.192798852920532</v>
+        <v>4.569432735443115</v>
       </c>
       <c r="G33" t="n">
-        <v>4.055176496505737</v>
+        <v>4.51011323928833</v>
       </c>
       <c r="H33" t="n">
-        <v>4.253195285797119</v>
+        <v>5.709974765777588</v>
       </c>
       <c r="I33" t="n">
-        <v>4.08907675743103</v>
+        <v>5.067620515823364</v>
       </c>
       <c r="J33" t="n">
-        <v>4.118011236190796</v>
+        <v>4.538465976715088</v>
       </c>
       <c r="K33" t="n">
-        <v>4.071137189865112</v>
+        <v>6.493481159210205</v>
       </c>
       <c r="L33" t="n">
-        <v>4.167986798286438</v>
+        <v>5.041879153251648</v>
       </c>
     </row>
     <row r="34">
@@ -3678,37 +3678,37 @@
         <v>39</v>
       </c>
       <c r="B34" t="n">
-        <v>3.754917621612549</v>
+        <v>4.583633422851562</v>
       </c>
       <c r="C34" t="n">
-        <v>3.518535375595093</v>
+        <v>4.196191787719727</v>
       </c>
       <c r="D34" t="n">
-        <v>3.912525415420532</v>
+        <v>4.068001508712769</v>
       </c>
       <c r="E34" t="n">
-        <v>3.82282543182373</v>
+        <v>3.800735235214233</v>
       </c>
       <c r="F34" t="n">
-        <v>3.564573287963867</v>
+        <v>3.710473775863647</v>
       </c>
       <c r="G34" t="n">
-        <v>3.6345374584198</v>
+        <v>3.678183555603027</v>
       </c>
       <c r="H34" t="n">
-        <v>3.644017934799194</v>
+        <v>4.007701396942139</v>
       </c>
       <c r="I34" t="n">
-        <v>3.504378080368042</v>
+        <v>3.89193868637085</v>
       </c>
       <c r="J34" t="n">
-        <v>3.444060087203979</v>
+        <v>4.006639957427979</v>
       </c>
       <c r="K34" t="n">
-        <v>3.675950765609741</v>
+        <v>4.04037070274353</v>
       </c>
       <c r="L34" t="n">
-        <v>3.647632145881653</v>
+        <v>3.998387002944946</v>
       </c>
     </row>
     <row r="35">
@@ -3716,37 +3716,37 @@
         <v>4</v>
       </c>
       <c r="B35" t="n">
-        <v>4.298300981521606</v>
+        <v>4.848934412002563</v>
       </c>
       <c r="C35" t="n">
-        <v>4.263900518417358</v>
+        <v>5.053873300552368</v>
       </c>
       <c r="D35" t="n">
-        <v>4.48581337928772</v>
+        <v>5.475095510482788</v>
       </c>
       <c r="E35" t="n">
-        <v>4.847381591796875</v>
+        <v>5.059881448745728</v>
       </c>
       <c r="F35" t="n">
-        <v>5.427892446517944</v>
+        <v>5.505902767181396</v>
       </c>
       <c r="G35" t="n">
-        <v>4.418002605438232</v>
+        <v>4.734144687652588</v>
       </c>
       <c r="H35" t="n">
-        <v>4.700799703598022</v>
+        <v>4.770956993103027</v>
       </c>
       <c r="I35" t="n">
-        <v>4.465896129608154</v>
+        <v>4.620254755020142</v>
       </c>
       <c r="J35" t="n">
-        <v>4.656884431838989</v>
+        <v>5.305434465408325</v>
       </c>
       <c r="K35" t="n">
-        <v>4.727715492248535</v>
+        <v>5.386733055114746</v>
       </c>
       <c r="L35" t="n">
-        <v>4.629258728027343</v>
+        <v>5.076121139526367</v>
       </c>
     </row>
     <row r="36">
@@ -3754,37 +3754,37 @@
         <v>40</v>
       </c>
       <c r="B36" t="n">
-        <v>3.257520437240601</v>
+        <v>3.519935607910156</v>
       </c>
       <c r="C36" t="n">
-        <v>3.209641218185425</v>
+        <v>3.824065685272217</v>
       </c>
       <c r="D36" t="n">
-        <v>3.320858716964722</v>
+        <v>3.815297842025757</v>
       </c>
       <c r="E36" t="n">
-        <v>3.338321924209595</v>
+        <v>3.773272037506104</v>
       </c>
       <c r="F36" t="n">
-        <v>3.357763528823853</v>
+        <v>3.773205280303955</v>
       </c>
       <c r="G36" t="n">
-        <v>3.348506212234497</v>
+        <v>3.536705017089844</v>
       </c>
       <c r="H36" t="n">
-        <v>3.346299648284912</v>
+        <v>3.854172229766846</v>
       </c>
       <c r="I36" t="n">
-        <v>3.418551206588745</v>
+        <v>3.830654859542847</v>
       </c>
       <c r="J36" t="n">
-        <v>3.305080890655518</v>
+        <v>3.797837495803833</v>
       </c>
       <c r="K36" t="n">
-        <v>3.179898262023926</v>
+        <v>4.087747573852539</v>
       </c>
       <c r="L36" t="n">
-        <v>3.308244204521179</v>
+        <v>3.78128936290741</v>
       </c>
     </row>
     <row r="37">
@@ -3792,37 +3792,37 @@
         <v>41</v>
       </c>
       <c r="B37" t="n">
-        <v>4.184841394424438</v>
+        <v>4.480959415435791</v>
       </c>
       <c r="C37" t="n">
-        <v>4.044205188751221</v>
+        <v>4.572917461395264</v>
       </c>
       <c r="D37" t="n">
-        <v>4.380354166030884</v>
+        <v>4.595441102981567</v>
       </c>
       <c r="E37" t="n">
-        <v>4.719026565551758</v>
+        <v>4.455255031585693</v>
       </c>
       <c r="F37" t="n">
-        <v>4.611264705657959</v>
+        <v>4.770488977432251</v>
       </c>
       <c r="G37" t="n">
-        <v>4.07062840461731</v>
+        <v>4.844874143600464</v>
       </c>
       <c r="H37" t="n">
-        <v>4.111023187637329</v>
+        <v>4.830118417739868</v>
       </c>
       <c r="I37" t="n">
-        <v>4.492175340652466</v>
+        <v>5.051363229751587</v>
       </c>
       <c r="J37" t="n">
-        <v>4.010589599609375</v>
+        <v>4.499180555343628</v>
       </c>
       <c r="K37" t="n">
-        <v>4.095852851867676</v>
+        <v>4.32996129989624</v>
       </c>
       <c r="L37" t="n">
-        <v>4.271996140480042</v>
+        <v>4.643055963516235</v>
       </c>
     </row>
     <row r="38">
@@ -3830,37 +3830,37 @@
         <v>42</v>
       </c>
       <c r="B38" t="n">
-        <v>3.996627330780029</v>
+        <v>4.861653566360474</v>
       </c>
       <c r="C38" t="n">
-        <v>4.266913652420044</v>
+        <v>4.56351375579834</v>
       </c>
       <c r="D38" t="n">
-        <v>4.355668783187866</v>
+        <v>4.654937028884888</v>
       </c>
       <c r="E38" t="n">
-        <v>4.048450946807861</v>
+        <v>4.550901889801025</v>
       </c>
       <c r="F38" t="n">
-        <v>4.346694946289062</v>
+        <v>4.416847467422485</v>
       </c>
       <c r="G38" t="n">
-        <v>3.957212448120117</v>
+        <v>4.922703742980957</v>
       </c>
       <c r="H38" t="n">
-        <v>4.35914945602417</v>
+        <v>4.435120820999146</v>
       </c>
       <c r="I38" t="n">
-        <v>4.098845958709717</v>
+        <v>4.358612060546875</v>
       </c>
       <c r="J38" t="n">
-        <v>4.557152271270752</v>
+        <v>4.874659061431885</v>
       </c>
       <c r="K38" t="n">
-        <v>4.472366571426392</v>
+        <v>4.812669038772583</v>
       </c>
       <c r="L38" t="n">
-        <v>4.245908236503601</v>
+        <v>4.645161843299865</v>
       </c>
     </row>
     <row r="39">
@@ -3868,37 +3868,37 @@
         <v>43</v>
       </c>
       <c r="B39" t="n">
-        <v>3.473083972930908</v>
+        <v>4.201644420623779</v>
       </c>
       <c r="C39" t="n">
-        <v>3.612601041793823</v>
+        <v>4.089523792266846</v>
       </c>
       <c r="D39" t="n">
-        <v>3.529373407363892</v>
+        <v>3.887253999710083</v>
       </c>
       <c r="E39" t="n">
-        <v>3.949724197387695</v>
+        <v>4.086190223693848</v>
       </c>
       <c r="F39" t="n">
-        <v>3.801110744476318</v>
+        <v>4.328883409500122</v>
       </c>
       <c r="G39" t="n">
-        <v>3.518365621566772</v>
+        <v>4.415571212768555</v>
       </c>
       <c r="H39" t="n">
-        <v>3.659481525421143</v>
+        <v>4.362654209136963</v>
       </c>
       <c r="I39" t="n">
-        <v>3.600621461868286</v>
+        <v>3.926201820373535</v>
       </c>
       <c r="J39" t="n">
-        <v>3.688902139663696</v>
+        <v>4.1272873878479</v>
       </c>
       <c r="K39" t="n">
-        <v>3.736777305603027</v>
+        <v>4.016946315765381</v>
       </c>
       <c r="L39" t="n">
-        <v>3.657004141807556</v>
+        <v>4.144215679168701</v>
       </c>
     </row>
     <row r="40">
@@ -3906,37 +3906,37 @@
         <v>44</v>
       </c>
       <c r="B40" t="n">
-        <v>4.329742670059204</v>
+        <v>4.827609062194824</v>
       </c>
       <c r="C40" t="n">
-        <v>4.366149187088013</v>
+        <v>4.492061376571655</v>
       </c>
       <c r="D40" t="n">
-        <v>4.349196672439575</v>
+        <v>4.428422451019287</v>
       </c>
       <c r="E40" t="n">
-        <v>4.164210319519043</v>
+        <v>4.560514211654663</v>
       </c>
       <c r="F40" t="n">
-        <v>4.356171131134033</v>
+        <v>4.540590286254883</v>
       </c>
       <c r="G40" t="n">
-        <v>4.025044441223145</v>
+        <v>4.518411159515381</v>
       </c>
       <c r="H40" t="n">
-        <v>4.328234910964966</v>
+        <v>4.564197301864624</v>
       </c>
       <c r="I40" t="n">
-        <v>4.093842267990112</v>
+        <v>4.786694526672363</v>
       </c>
       <c r="J40" t="n">
-        <v>4.174619913101196</v>
+        <v>4.778598308563232</v>
       </c>
       <c r="K40" t="n">
-        <v>4.499803304672241</v>
+        <v>5.003377437591553</v>
       </c>
       <c r="L40" t="n">
-        <v>4.268701481819153</v>
+        <v>4.650047612190247</v>
       </c>
     </row>
     <row r="41">
@@ -3944,37 +3944,37 @@
         <v>45</v>
       </c>
       <c r="B41" t="n">
-        <v>3.789169073104858</v>
+        <v>4.363863229751587</v>
       </c>
       <c r="C41" t="n">
-        <v>4.008580207824707</v>
+        <v>4.678812265396118</v>
       </c>
       <c r="D41" t="n">
-        <v>4.379624366760254</v>
+        <v>4.491634607315063</v>
       </c>
       <c r="E41" t="n">
-        <v>3.904345989227295</v>
+        <v>6.088969707489014</v>
       </c>
       <c r="F41" t="n">
-        <v>3.93027138710022</v>
+        <v>4.452754735946655</v>
       </c>
       <c r="G41" t="n">
-        <v>4.112810850143433</v>
+        <v>4.720112323760986</v>
       </c>
       <c r="H41" t="n">
-        <v>3.907325506210327</v>
+        <v>4.488019704818726</v>
       </c>
       <c r="I41" t="n">
-        <v>4.371142864227295</v>
+        <v>4.725699186325073</v>
       </c>
       <c r="J41" t="n">
-        <v>3.995629787445068</v>
+        <v>4.292083978652954</v>
       </c>
       <c r="K41" t="n">
-        <v>4.150213241577148</v>
+        <v>4.583841562271118</v>
       </c>
       <c r="L41" t="n">
-        <v>4.054911327362061</v>
+        <v>4.688579130172729</v>
       </c>
     </row>
     <row r="42">
@@ -3982,37 +3982,37 @@
         <v>46</v>
       </c>
       <c r="B42" t="n">
-        <v>3.962690830230713</v>
+        <v>4.867968082427979</v>
       </c>
       <c r="C42" t="n">
-        <v>4.09485387802124</v>
+        <v>4.57518458366394</v>
       </c>
       <c r="D42" t="n">
-        <v>3.907328605651855</v>
+        <v>4.378683805465698</v>
       </c>
       <c r="E42" t="n">
-        <v>3.875905990600586</v>
+        <v>4.454172372817993</v>
       </c>
       <c r="F42" t="n">
-        <v>4.294341802597046</v>
+        <v>4.2669358253479</v>
       </c>
       <c r="G42" t="n">
-        <v>3.85049295425415</v>
+        <v>4.392972707748413</v>
       </c>
       <c r="H42" t="n">
-        <v>3.962174415588379</v>
+        <v>4.263768434524536</v>
       </c>
       <c r="I42" t="n">
-        <v>3.95770525932312</v>
+        <v>4.377429962158203</v>
       </c>
       <c r="J42" t="n">
-        <v>3.922281742095947</v>
+        <v>4.623944520950317</v>
       </c>
       <c r="K42" t="n">
-        <v>4.454414129257202</v>
+        <v>4.403395414352417</v>
       </c>
       <c r="L42" t="n">
-        <v>4.028218960762024</v>
+        <v>4.46044557094574</v>
       </c>
     </row>
     <row r="43">
@@ -4020,37 +4020,37 @@
         <v>47</v>
       </c>
       <c r="B43" t="n">
-        <v>4.080896615982056</v>
+        <v>5.268357992172241</v>
       </c>
       <c r="C43" t="n">
-        <v>4.023522853851318</v>
+        <v>4.863107204437256</v>
       </c>
       <c r="D43" t="n">
-        <v>4.649929285049438</v>
+        <v>5.079889535903931</v>
       </c>
       <c r="E43" t="n">
-        <v>4.002634763717651</v>
+        <v>4.641513586044312</v>
       </c>
       <c r="F43" t="n">
-        <v>4.678332805633545</v>
+        <v>5.004851579666138</v>
       </c>
       <c r="G43" t="n">
-        <v>4.022536039352417</v>
+        <v>4.799660921096802</v>
       </c>
       <c r="H43" t="n">
-        <v>4.410517930984497</v>
+        <v>5.291806221008301</v>
       </c>
       <c r="I43" t="n">
-        <v>4.092859983444214</v>
+        <v>4.495405912399292</v>
       </c>
       <c r="J43" t="n">
-        <v>4.228020191192627</v>
+        <v>4.598112344741821</v>
       </c>
       <c r="K43" t="n">
-        <v>4.316267251968384</v>
+        <v>4.321429967880249</v>
       </c>
       <c r="L43" t="n">
-        <v>4.250551772117615</v>
+        <v>4.836413526535035</v>
       </c>
     </row>
     <row r="44">
@@ -4058,37 +4058,37 @@
         <v>48</v>
       </c>
       <c r="B44" t="n">
-        <v>4.14324426651001</v>
+        <v>4.295779466629028</v>
       </c>
       <c r="C44" t="n">
-        <v>3.885911703109741</v>
+        <v>4.556321382522583</v>
       </c>
       <c r="D44" t="n">
-        <v>4.191101551055908</v>
+        <v>4.316253662109375</v>
       </c>
       <c r="E44" t="n">
-        <v>3.981668472290039</v>
+        <v>4.459754228591919</v>
       </c>
       <c r="F44" t="n">
-        <v>3.845012903213501</v>
+        <v>4.540543079376221</v>
       </c>
       <c r="G44" t="n">
-        <v>3.824052572250366</v>
+        <v>4.616768836975098</v>
       </c>
       <c r="H44" t="n">
-        <v>4.369650840759277</v>
+        <v>4.457072973251343</v>
       </c>
       <c r="I44" t="n">
-        <v>4.064936637878418</v>
+        <v>4.610250234603882</v>
       </c>
       <c r="J44" t="n">
-        <v>3.932260274887085</v>
+        <v>4.269508361816406</v>
       </c>
       <c r="K44" t="n">
-        <v>3.886399745941162</v>
+        <v>4.369717359542847</v>
       </c>
       <c r="L44" t="n">
-        <v>4.012423896789551</v>
+        <v>4.44919695854187</v>
       </c>
     </row>
     <row r="45">
@@ -4096,37 +4096,37 @@
         <v>49</v>
       </c>
       <c r="B45" t="n">
-        <v>3.777693748474121</v>
+        <v>4.238959074020386</v>
       </c>
       <c r="C45" t="n">
-        <v>3.693881273269653</v>
+        <v>4.166197061538696</v>
       </c>
       <c r="D45" t="n">
-        <v>3.763206243515015</v>
+        <v>4.273235082626343</v>
       </c>
       <c r="E45" t="n">
-        <v>3.675429344177246</v>
+        <v>4.241782665252686</v>
       </c>
       <c r="F45" t="n">
-        <v>3.844513654708862</v>
+        <v>4.299537897109985</v>
       </c>
       <c r="G45" t="n">
-        <v>3.802105903625488</v>
+        <v>4.528309345245361</v>
       </c>
       <c r="H45" t="n">
-        <v>3.768678903579712</v>
+        <v>4.078589200973511</v>
       </c>
       <c r="I45" t="n">
-        <v>3.786139488220215</v>
+        <v>4.27847957611084</v>
       </c>
       <c r="J45" t="n">
-        <v>3.828043937683105</v>
+        <v>4.234630346298218</v>
       </c>
       <c r="K45" t="n">
-        <v>3.642084360122681</v>
+        <v>4.242672681808472</v>
       </c>
       <c r="L45" t="n">
-        <v>3.75817768573761</v>
+        <v>4.25823929309845</v>
       </c>
     </row>
     <row r="46">
@@ -4134,37 +4134,37 @@
         <v>5</v>
       </c>
       <c r="B46" t="n">
-        <v>3.801102638244629</v>
+        <v>4.313663482666016</v>
       </c>
       <c r="C46" t="n">
-        <v>3.697379350662231</v>
+        <v>4.425097703933716</v>
       </c>
       <c r="D46" t="n">
-        <v>4.06593656539917</v>
+        <v>4.333979845046997</v>
       </c>
       <c r="E46" t="n">
-        <v>3.952235698699951</v>
+        <v>3.988576650619507</v>
       </c>
       <c r="F46" t="n">
-        <v>4.156210422515869</v>
+        <v>4.327649354934692</v>
       </c>
       <c r="G46" t="n">
-        <v>4.688286781311035</v>
+        <v>4.595394849777222</v>
       </c>
       <c r="H46" t="n">
-        <v>3.802131652832031</v>
+        <v>4.158479452133179</v>
       </c>
       <c r="I46" t="n">
-        <v>4.539684772491455</v>
+        <v>5.180526733398438</v>
       </c>
       <c r="J46" t="n">
-        <v>3.987616539001465</v>
+        <v>4.340242385864258</v>
       </c>
       <c r="K46" t="n">
-        <v>3.94621753692627</v>
+        <v>4.39100456237793</v>
       </c>
       <c r="L46" t="n">
-        <v>4.063680195808411</v>
+        <v>4.405461502075195</v>
       </c>
     </row>
     <row r="47">
@@ -4172,37 +4172,37 @@
         <v>50</v>
       </c>
       <c r="B47" t="n">
-        <v>4.099841833114624</v>
+        <v>4.355888605117798</v>
       </c>
       <c r="C47" t="n">
-        <v>4.671353578567505</v>
+        <v>4.680038690567017</v>
       </c>
       <c r="D47" t="n">
-        <v>4.43348240852356</v>
+        <v>4.784138917922974</v>
       </c>
       <c r="E47" t="n">
-        <v>3.798106670379639</v>
+        <v>5.137650728225708</v>
       </c>
       <c r="F47" t="n">
-        <v>3.795180797576904</v>
+        <v>4.692228555679321</v>
       </c>
       <c r="G47" t="n">
-        <v>4.085373878479004</v>
+        <v>4.552115917205811</v>
       </c>
       <c r="H47" t="n">
-        <v>4.099834442138672</v>
+        <v>4.57732367515564</v>
       </c>
       <c r="I47" t="n">
-        <v>4.376628160476685</v>
+        <v>4.408785343170166</v>
       </c>
       <c r="J47" t="n">
-        <v>4.823464870452881</v>
+        <v>4.617231369018555</v>
       </c>
       <c r="K47" t="n">
-        <v>3.816067695617676</v>
+        <v>5.247593879699707</v>
       </c>
       <c r="L47" t="n">
-        <v>4.199933433532715</v>
+        <v>4.70529956817627</v>
       </c>
     </row>
     <row r="48">
@@ -4210,37 +4210,37 @@
         <v>6</v>
       </c>
       <c r="B48" t="n">
-        <v>4.185124158859253</v>
+        <v>4.493827104568481</v>
       </c>
       <c r="C48" t="n">
-        <v>4.013578176498413</v>
+        <v>4.495358943939209</v>
       </c>
       <c r="D48" t="n">
-        <v>4.160693883895874</v>
+        <v>4.479750394821167</v>
       </c>
       <c r="E48" t="n">
-        <v>4.152199745178223</v>
+        <v>4.595966577529907</v>
       </c>
       <c r="F48" t="n">
-        <v>4.071412563323975</v>
+        <v>4.559377670288086</v>
       </c>
       <c r="G48" t="n">
-        <v>4.123276948928833</v>
+        <v>4.800045013427734</v>
       </c>
       <c r="H48" t="n">
-        <v>4.135733366012573</v>
+        <v>4.29628586769104</v>
       </c>
       <c r="I48" t="n">
-        <v>4.101835012435913</v>
+        <v>5.010217189788818</v>
       </c>
       <c r="J48" t="n">
-        <v>4.170658111572266</v>
+        <v>4.40545916557312</v>
       </c>
       <c r="K48" t="n">
-        <v>4.204046964645386</v>
+        <v>4.642244338989258</v>
       </c>
       <c r="L48" t="n">
-        <v>4.131855893135071</v>
+        <v>4.577853226661682</v>
       </c>
     </row>
     <row r="49">
@@ -4248,37 +4248,37 @@
         <v>7</v>
       </c>
       <c r="B49" t="n">
-        <v>4.700257301330566</v>
+        <v>4.745338439941406</v>
       </c>
       <c r="C49" t="n">
-        <v>4.321269512176514</v>
+        <v>4.949512958526611</v>
       </c>
       <c r="D49" t="n">
-        <v>4.135645389556885</v>
+        <v>4.626668453216553</v>
       </c>
       <c r="E49" t="n">
-        <v>4.543940305709839</v>
+        <v>4.740960359573364</v>
       </c>
       <c r="F49" t="n">
-        <v>4.203282594680786</v>
+        <v>4.632764339447021</v>
       </c>
       <c r="G49" t="n">
-        <v>3.921496868133545</v>
+        <v>4.814432859420776</v>
       </c>
       <c r="H49" t="n">
-        <v>4.720475435256958</v>
+        <v>4.612756013870239</v>
       </c>
       <c r="I49" t="n">
-        <v>4.46613073348999</v>
+        <v>4.620353937149048</v>
       </c>
       <c r="J49" t="n">
-        <v>4.081580400466919</v>
+        <v>4.78419828414917</v>
       </c>
       <c r="K49" t="n">
-        <v>4.718483209609985</v>
+        <v>5.294337034225464</v>
       </c>
       <c r="L49" t="n">
-        <v>4.381256175041199</v>
+        <v>4.782132267951965</v>
       </c>
     </row>
     <row r="50">
@@ -4286,37 +4286,37 @@
         <v>8</v>
       </c>
       <c r="B50" t="n">
-        <v>3.377399921417236</v>
+        <v>4.407795667648315</v>
       </c>
       <c r="C50" t="n">
-        <v>3.284122705459595</v>
+        <v>3.836097240447998</v>
       </c>
       <c r="D50" t="n">
-        <v>3.352941751480103</v>
+        <v>3.875920057296753</v>
       </c>
       <c r="E50" t="n">
-        <v>3.717932939529419</v>
+        <v>4.259036779403687</v>
       </c>
       <c r="F50" t="n">
-        <v>3.517368316650391</v>
+        <v>3.814191341400146</v>
       </c>
       <c r="G50" t="n">
-        <v>3.57974648475647</v>
+        <v>4.163865566253662</v>
       </c>
       <c r="H50" t="n">
-        <v>4.141773700714111</v>
+        <v>3.936798095703125</v>
       </c>
       <c r="I50" t="n">
-        <v>4.032078742980957</v>
+        <v>4.093121290206909</v>
       </c>
       <c r="J50" t="n">
-        <v>3.808150053024292</v>
+        <v>3.649580717086792</v>
       </c>
       <c r="K50" t="n">
-        <v>3.804178476333618</v>
+        <v>3.727794170379639</v>
       </c>
       <c r="L50" t="n">
-        <v>3.661569309234619</v>
+        <v>3.976420092582702</v>
       </c>
     </row>
     <row r="51">
@@ -4324,37 +4324,37 @@
         <v>9</v>
       </c>
       <c r="B51" t="n">
-        <v>4.39016318321228</v>
+        <v>4.51751446723938</v>
       </c>
       <c r="C51" t="n">
-        <v>4.055943727493286</v>
+        <v>4.543795824050903</v>
       </c>
       <c r="D51" t="n">
-        <v>3.811076641082764</v>
+        <v>4.658846855163574</v>
       </c>
       <c r="E51" t="n">
-        <v>4.163171768188477</v>
+        <v>4.923222303390503</v>
       </c>
       <c r="F51" t="n">
-        <v>3.865938186645508</v>
+        <v>5.012663841247559</v>
       </c>
       <c r="G51" t="n">
-        <v>3.773606061935425</v>
+        <v>4.559053421020508</v>
       </c>
       <c r="H51" t="n">
-        <v>3.952442646026611</v>
+        <v>6.79546070098877</v>
       </c>
       <c r="I51" t="n">
-        <v>3.7893385887146</v>
+        <v>4.828362703323364</v>
       </c>
       <c r="J51" t="n">
-        <v>4.08011531829834</v>
+        <v>6.253916501998901</v>
       </c>
       <c r="K51" t="n">
-        <v>3.814262390136719</v>
+        <v>5.697853326797485</v>
       </c>
       <c r="L51" t="n">
-        <v>3.969605851173401</v>
+        <v>5.179068994522095</v>
       </c>
     </row>
     <row r="52">
@@ -4364,37 +4364,37 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>4.044869136810303</v>
+        <v>4.604934191703796</v>
       </c>
       <c r="C52" t="n">
-        <v>4.066148238182068</v>
+        <v>4.529068269729614</v>
       </c>
       <c r="D52" t="n">
-        <v>4.054194521903992</v>
+        <v>4.493432774543762</v>
       </c>
       <c r="E52" t="n">
-        <v>4.086396689414978</v>
+        <v>4.61508394241333</v>
       </c>
       <c r="F52" t="n">
-        <v>4.078882007598877</v>
+        <v>4.555992507934571</v>
       </c>
       <c r="G52" t="n">
-        <v>4.036415648460388</v>
+        <v>4.560469279289245</v>
       </c>
       <c r="H52" t="n">
-        <v>4.101598863601684</v>
+        <v>4.627599334716797</v>
       </c>
       <c r="I52" t="n">
-        <v>4.11177586555481</v>
+        <v>4.60774739742279</v>
       </c>
       <c r="J52" t="n">
-        <v>4.125343866348267</v>
+        <v>4.56915018081665</v>
       </c>
       <c r="K52" t="n">
-        <v>4.128737607002258</v>
+        <v>4.62867169380188</v>
       </c>
       <c r="L52" t="n">
-        <v>4.083436244487762</v>
+        <v>4.579214957237244</v>
       </c>
     </row>
   </sheetData>
